--- a/2023/搜索量(2023).xlsx
+++ b/2023/搜索量(2023).xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="百度指数" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,24 @@
     <sheet name="百度指数原始数据" sheetId="2" r:id="rId3"/>
     <sheet name="谷歌趋势原始数据" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
     <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1187,14 +1197,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1233,59 +1243,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1299,8 +1259,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1316,31 +1283,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1356,9 +1315,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1370,8 +1329,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1386,7 +1396,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1398,13 +1432,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1416,37 +1444,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1464,73 +1474,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1548,19 +1492,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1589,11 +1599,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1607,17 +1623,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1654,6 +1679,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1662,181 +1696,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1846,10 +1856,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1867,19 +1877,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1891,54 +1898,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1947,452 +1954,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="multiTimeline (1)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3" t="str">
-            <v>周</v>
-          </cell>
-          <cell r="J3" t="str">
-            <v>Energy internet: (全球)</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>44927</v>
-          </cell>
-          <cell r="J4">
-            <v>79</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>44927</v>
-          </cell>
-          <cell r="J5">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>44927</v>
-          </cell>
-          <cell r="J6">
-            <v>90</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>44927</v>
-          </cell>
-          <cell r="J7">
-            <v>90</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>44927</v>
-          </cell>
-          <cell r="J8">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="I9">
-            <v>44958</v>
-          </cell>
-          <cell r="J9">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="I10">
-            <v>44958</v>
-          </cell>
-          <cell r="J10">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="I11">
-            <v>44958</v>
-          </cell>
-          <cell r="J11">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="I12">
-            <v>44958</v>
-          </cell>
-          <cell r="J12">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="I13">
-            <v>44986</v>
-          </cell>
-          <cell r="J13">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="I14">
-            <v>44986</v>
-          </cell>
-          <cell r="J14">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="I15">
-            <v>44986</v>
-          </cell>
-          <cell r="J15">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="I16">
-            <v>44986</v>
-          </cell>
-          <cell r="J16">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="I17">
-            <v>45017</v>
-          </cell>
-          <cell r="J17">
-            <v>88</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="I18">
-            <v>45017</v>
-          </cell>
-          <cell r="J18">
-            <v>84</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="I19">
-            <v>45017</v>
-          </cell>
-          <cell r="J19">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="I20">
-            <v>45017</v>
-          </cell>
-          <cell r="J20">
-            <v>97</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="I21">
-            <v>45017</v>
-          </cell>
-          <cell r="J21">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="I22">
-            <v>45047</v>
-          </cell>
-          <cell r="J22">
-            <v>96</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="I23">
-            <v>45047</v>
-          </cell>
-          <cell r="J23">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="I24">
-            <v>45047</v>
-          </cell>
-          <cell r="J24">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="I25">
-            <v>45047</v>
-          </cell>
-          <cell r="J25">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="I26">
-            <v>45078</v>
-          </cell>
-          <cell r="J26">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="I27">
-            <v>45078</v>
-          </cell>
-          <cell r="J27">
-            <v>88</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="I28">
-            <v>45078</v>
-          </cell>
-          <cell r="J28">
-            <v>89</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="I29">
-            <v>45078</v>
-          </cell>
-          <cell r="J29">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="I30">
-            <v>45108</v>
-          </cell>
-          <cell r="J30">
-            <v>81</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="I31">
-            <v>45108</v>
-          </cell>
-          <cell r="J31">
-            <v>94</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="I32">
-            <v>45108</v>
-          </cell>
-          <cell r="J32">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="I33">
-            <v>45108</v>
-          </cell>
-          <cell r="J33">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="I34">
-            <v>45108</v>
-          </cell>
-          <cell r="J34">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="I35">
-            <v>45139</v>
-          </cell>
-          <cell r="J35">
-            <v>79</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="I36">
-            <v>45139</v>
-          </cell>
-          <cell r="J36">
-            <v>74</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="I37">
-            <v>45139</v>
-          </cell>
-          <cell r="J37">
-            <v>68</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="I38">
-            <v>45139</v>
-          </cell>
-          <cell r="J38">
-            <v>89</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="I39">
-            <v>45170</v>
-          </cell>
-          <cell r="J39">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="I40">
-            <v>45170</v>
-          </cell>
-          <cell r="J40">
-            <v>88</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="I41">
-            <v>45170</v>
-          </cell>
-          <cell r="J41">
-            <v>91</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="I42">
-            <v>45170</v>
-          </cell>
-          <cell r="J42">
-            <v>89</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="I43">
-            <v>45200</v>
-          </cell>
-          <cell r="J43">
-            <v>93</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="I44">
-            <v>45200</v>
-          </cell>
-          <cell r="J44">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="I45">
-            <v>45200</v>
-          </cell>
-          <cell r="J45">
-            <v>89</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="I46">
-            <v>45200</v>
-          </cell>
-          <cell r="J46">
-            <v>75</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="I47">
-            <v>45200</v>
-          </cell>
-          <cell r="J47">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="I48">
-            <v>45231</v>
-          </cell>
-          <cell r="J48">
-            <v>90</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="I49">
-            <v>45231</v>
-          </cell>
-          <cell r="J49">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="I50">
-            <v>45231</v>
-          </cell>
-          <cell r="J50">
-            <v>77</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="I51">
-            <v>45231</v>
-          </cell>
-          <cell r="J51">
-            <v>90</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="I52">
-            <v>45261</v>
-          </cell>
-          <cell r="J52">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="I53">
-            <v>45261</v>
-          </cell>
-          <cell r="J53">
-            <v>84</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="I54">
-            <v>45261</v>
-          </cell>
-          <cell r="J54">
-            <v>78</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="I55">
-            <v>45261</v>
-          </cell>
-          <cell r="J55">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="I56">
-            <v>45261</v>
-          </cell>
-          <cell r="J56">
-            <v>84</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2933,7 +2494,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Energy internet: (全球)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="61" maxValue="100" count="21">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="100" count="21">
         <n v="79"/>
         <n v="95"/>
         <n v="90"/>
@@ -5951,12 +5512,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="15.2307692307692" defaultRowHeight="17.6" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="15.2300884955752" defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="16384" width="15.2307692307692" style="15"/>
+    <col min="1" max="16384" width="15.2300884955752" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" ht="20.4" spans="1:2">
+    <row r="1" s="9" customFormat="1" ht="17.6" spans="1:2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -5964,7 +5525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="15" customFormat="1" spans="1:2">
+    <row r="2" s="14" customFormat="1" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5972,7 +5533,7 @@
         <v>4592</v>
       </c>
     </row>
-    <row r="3" s="15" customFormat="1" spans="1:2">
+    <row r="3" s="14" customFormat="1" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5980,7 +5541,7 @@
         <v>5021</v>
       </c>
     </row>
-    <row r="4" s="15" customFormat="1" spans="1:2">
+    <row r="4" s="14" customFormat="1" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5988,7 +5549,7 @@
         <v>5857</v>
       </c>
     </row>
-    <row r="5" s="15" customFormat="1" spans="1:2">
+    <row r="5" s="14" customFormat="1" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5996,7 +5557,7 @@
         <v>5596</v>
       </c>
     </row>
-    <row r="6" s="15" customFormat="1" spans="1:2">
+    <row r="6" s="14" customFormat="1" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6004,7 +5565,7 @@
         <v>5172</v>
       </c>
     </row>
-    <row r="7" s="15" customFormat="1" spans="1:2">
+    <row r="7" s="14" customFormat="1" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -6012,7 +5573,7 @@
         <v>5516</v>
       </c>
     </row>
-    <row r="8" s="15" customFormat="1" spans="1:2">
+    <row r="8" s="14" customFormat="1" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6020,7 +5581,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="9" s="15" customFormat="1" spans="1:2">
+    <row r="9" s="14" customFormat="1" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6028,7 +5589,7 @@
         <v>5019</v>
       </c>
     </row>
-    <row r="10" s="15" customFormat="1" spans="1:2">
+    <row r="10" s="14" customFormat="1" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -6036,7 +5597,7 @@
         <v>5113</v>
       </c>
     </row>
-    <row r="11" s="15" customFormat="1" spans="1:2">
+    <row r="11" s="14" customFormat="1" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -6044,7 +5605,7 @@
         <v>4989</v>
       </c>
     </row>
-    <row r="12" s="15" customFormat="1" spans="1:2">
+    <row r="12" s="14" customFormat="1" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -6052,11 +5613,11 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="13" s="15" customFormat="1" spans="1:2">
-      <c r="A13" s="16" t="s">
+    <row r="13" s="14" customFormat="1" spans="1:2">
+      <c r="A13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="15">
         <v>4559</v>
       </c>
     </row>
@@ -6070,14 +5631,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O366"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23008849557522" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="23.2307692307692" style="7" customWidth="1"/>
-    <col min="5" max="5" width="12.0769230769231" customWidth="1"/>
-    <col min="10" max="11" width="31.0769230769231"/>
+    <col min="1" max="1" width="23.2300884955752" style="7" customWidth="1"/>
+    <col min="5" max="5" width="12.0796460176991" customWidth="1"/>
+    <col min="10" max="11" width="31.0796460176991"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" ht="20.4" spans="1:15">
+    <row r="1" s="6" customFormat="1" ht="17.6" spans="1:15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6095,9 +5656,9 @@
       <c r="B2">
         <v>451</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="2"/>
-      <c r="N2" s="14"/>
+      <c r="N2" s="11"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15">
@@ -6107,9 +5668,9 @@
       <c r="B3">
         <v>386</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="2"/>
-      <c r="N3" s="14"/>
+      <c r="N3" s="11"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15">
@@ -6119,9 +5680,9 @@
       <c r="B4">
         <v>374</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="10"/>
       <c r="F4" s="2"/>
-      <c r="N4" s="14"/>
+      <c r="N4" s="11"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15">
@@ -6131,9 +5692,9 @@
       <c r="B5">
         <v>449</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="2"/>
-      <c r="N5" s="14"/>
+      <c r="N5" s="11"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15">
@@ -6143,9 +5704,9 @@
       <c r="B6">
         <v>372</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="2"/>
-      <c r="N6" s="14"/>
+      <c r="N6" s="11"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15">
@@ -6155,9 +5716,9 @@
       <c r="B7">
         <v>365</v>
       </c>
-      <c r="E7" s="13"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="2"/>
-      <c r="N7" s="14"/>
+      <c r="N7" s="11"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15">
@@ -6167,9 +5728,9 @@
       <c r="B8">
         <v>431</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="2"/>
-      <c r="N8" s="14"/>
+      <c r="N8" s="11"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15">
@@ -6179,9 +5740,9 @@
       <c r="B9">
         <v>310</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="2"/>
-      <c r="N9" s="14"/>
+      <c r="N9" s="11"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15">
@@ -6191,9 +5752,9 @@
       <c r="B10">
         <v>348</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="2"/>
-      <c r="N10" s="14"/>
+      <c r="N10" s="11"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15">
@@ -6203,9 +5764,9 @@
       <c r="B11">
         <v>419</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="2"/>
-      <c r="N11" s="14"/>
+      <c r="N11" s="11"/>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15">
@@ -6215,1204 +5776,1204 @@
       <c r="B12">
         <v>342</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="2"/>
-      <c r="N12" s="14"/>
+      <c r="N12" s="11"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="13">
         <v>392</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="2"/>
-      <c r="N13" s="14"/>
+      <c r="N13" s="11"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" ht="19.6" spans="1:15">
-      <c r="A14" s="12"/>
+    <row r="14" ht="20.25" spans="1:15">
+      <c r="A14" s="5"/>
       <c r="F14" s="2"/>
-      <c r="N14" s="14"/>
+      <c r="N14" s="11"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" ht="19.6" spans="1:15">
-      <c r="A15" s="12"/>
+    <row r="15" ht="20.25" spans="1:15">
+      <c r="A15" s="5"/>
       <c r="F15" s="2"/>
-      <c r="N15" s="14"/>
+      <c r="N15" s="11"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" ht="19.6" spans="1:15">
-      <c r="A16" s="12"/>
+    <row r="16" ht="20.25" spans="1:15">
+      <c r="A16" s="5"/>
       <c r="F16" s="2"/>
-      <c r="N16" s="14"/>
+      <c r="N16" s="11"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" ht="19.6" spans="1:15">
-      <c r="A17" s="12"/>
+    <row r="17" ht="20.25" spans="1:15">
+      <c r="A17" s="5"/>
       <c r="F17" s="2"/>
-      <c r="N17" s="14"/>
+      <c r="N17" s="11"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" ht="19.6" spans="1:15">
-      <c r="A18" s="12"/>
+    <row r="18" ht="20.25" spans="1:15">
+      <c r="A18" s="5"/>
       <c r="F18" s="2"/>
-      <c r="N18" s="14"/>
+      <c r="N18" s="11"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" ht="19.6" spans="1:15">
-      <c r="A19" s="12"/>
+    <row r="19" ht="20.25" spans="1:15">
+      <c r="A19" s="5"/>
       <c r="F19" s="2"/>
-      <c r="N19" s="14"/>
+      <c r="N19" s="11"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" ht="19.6" spans="1:15">
-      <c r="A20" s="12"/>
+    <row r="20" ht="20.25" spans="1:15">
+      <c r="A20" s="5"/>
       <c r="F20" s="2"/>
-      <c r="N20" s="14"/>
+      <c r="N20" s="11"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" ht="19.6" spans="1:15">
-      <c r="A21" s="12"/>
+    <row r="21" ht="20.25" spans="1:15">
+      <c r="A21" s="5"/>
       <c r="F21" s="2"/>
-      <c r="N21" s="14"/>
+      <c r="N21" s="11"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" ht="19.6" spans="1:15">
-      <c r="A22" s="12"/>
+    <row r="22" ht="20.25" spans="1:15">
+      <c r="A22" s="5"/>
       <c r="F22" s="2"/>
-      <c r="N22" s="14"/>
+      <c r="N22" s="11"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" ht="19.6" spans="1:15">
-      <c r="A23" s="12"/>
+    <row r="23" ht="20.25" spans="1:15">
+      <c r="A23" s="5"/>
       <c r="F23" s="2"/>
-      <c r="N23" s="14"/>
+      <c r="N23" s="11"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" ht="19.6" spans="1:15">
-      <c r="A24" s="12"/>
+    <row r="24" ht="20.25" spans="1:15">
+      <c r="A24" s="5"/>
       <c r="F24" s="2"/>
-      <c r="N24" s="14"/>
+      <c r="N24" s="11"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" ht="19.6" spans="1:15">
-      <c r="A25" s="12"/>
+    <row r="25" ht="20.25" spans="1:15">
+      <c r="A25" s="5"/>
       <c r="F25" s="2"/>
-      <c r="N25" s="14"/>
+      <c r="N25" s="11"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" ht="19.6" spans="1:15">
-      <c r="A26" s="12"/>
+    <row r="26" ht="20.25" spans="1:15">
+      <c r="A26" s="5"/>
       <c r="F26" s="2"/>
-      <c r="N26" s="14"/>
+      <c r="N26" s="11"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" ht="19.6" spans="1:15">
-      <c r="A27" s="12"/>
+    <row r="27" ht="20.25" spans="1:15">
+      <c r="A27" s="5"/>
       <c r="F27" s="2"/>
-      <c r="N27" s="14"/>
+      <c r="N27" s="11"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" ht="19.6" spans="1:15">
-      <c r="A28" s="12"/>
+    <row r="28" ht="20.25" spans="1:15">
+      <c r="A28" s="5"/>
       <c r="F28" s="2"/>
-      <c r="N28" s="14"/>
+      <c r="N28" s="11"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" ht="19.6" spans="1:15">
-      <c r="A29" s="12"/>
+    <row r="29" ht="20.25" spans="1:15">
+      <c r="A29" s="5"/>
       <c r="F29" s="2"/>
-      <c r="N29" s="14"/>
+      <c r="N29" s="11"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" ht="19.6" spans="1:15">
-      <c r="A30" s="12"/>
+    <row r="30" ht="20.25" spans="1:15">
+      <c r="A30" s="5"/>
       <c r="F30" s="2"/>
-      <c r="N30" s="14"/>
+      <c r="N30" s="11"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" ht="19.6" spans="1:15">
-      <c r="A31" s="12"/>
+    <row r="31" ht="20.25" spans="1:15">
+      <c r="A31" s="5"/>
       <c r="F31" s="2"/>
-      <c r="N31" s="14"/>
+      <c r="N31" s="11"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" ht="19.6" spans="1:15">
-      <c r="A32" s="12"/>
+    <row r="32" ht="20.25" spans="1:15">
+      <c r="A32" s="5"/>
       <c r="F32" s="2"/>
-      <c r="N32" s="14"/>
+      <c r="N32" s="11"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" ht="19.6" spans="1:15">
-      <c r="A33" s="12"/>
+    <row r="33" ht="20.25" spans="1:15">
+      <c r="A33" s="5"/>
       <c r="F33" s="2"/>
-      <c r="N33" s="14"/>
+      <c r="N33" s="11"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" ht="19.6" spans="1:15">
-      <c r="A34" s="12"/>
+    <row r="34" ht="20.25" spans="1:15">
+      <c r="A34" s="5"/>
       <c r="F34" s="2"/>
-      <c r="N34" s="14"/>
+      <c r="N34" s="11"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" ht="19.6" spans="1:15">
-      <c r="A35" s="12"/>
+    <row r="35" ht="20.25" spans="1:15">
+      <c r="A35" s="5"/>
       <c r="F35" s="2"/>
-      <c r="N35" s="14"/>
+      <c r="N35" s="11"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" ht="19.6" spans="1:15">
-      <c r="A36" s="12"/>
+    <row r="36" ht="20.25" spans="1:15">
+      <c r="A36" s="5"/>
       <c r="F36" s="2"/>
-      <c r="N36" s="14"/>
+      <c r="N36" s="11"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" ht="19.6" spans="1:15">
-      <c r="A37" s="12"/>
+    <row r="37" ht="20.25" spans="1:15">
+      <c r="A37" s="5"/>
       <c r="F37" s="2"/>
-      <c r="N37" s="14"/>
+      <c r="N37" s="11"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" ht="19.6" spans="1:15">
-      <c r="A38" s="12"/>
+    <row r="38" ht="20.25" spans="1:15">
+      <c r="A38" s="5"/>
       <c r="F38" s="2"/>
-      <c r="N38" s="14"/>
+      <c r="N38" s="11"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" ht="19.6" spans="1:15">
-      <c r="A39" s="12"/>
+    <row r="39" ht="20.25" spans="1:15">
+      <c r="A39" s="5"/>
       <c r="F39" s="2"/>
-      <c r="N39" s="14"/>
+      <c r="N39" s="11"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" ht="19.6" spans="1:15">
-      <c r="A40" s="12"/>
+    <row r="40" ht="20.25" spans="1:15">
+      <c r="A40" s="5"/>
       <c r="F40" s="2"/>
-      <c r="N40" s="14"/>
+      <c r="N40" s="11"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" ht="19.6" spans="1:15">
-      <c r="A41" s="12"/>
+    <row r="41" ht="20.25" spans="1:15">
+      <c r="A41" s="5"/>
       <c r="F41" s="2"/>
-      <c r="N41" s="14"/>
+      <c r="N41" s="11"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" ht="19.6" spans="1:15">
-      <c r="A42" s="12"/>
+    <row r="42" ht="20.25" spans="1:15">
+      <c r="A42" s="5"/>
       <c r="F42" s="2"/>
-      <c r="N42" s="14"/>
+      <c r="N42" s="11"/>
       <c r="O42" s="2"/>
     </row>
-    <row r="43" ht="19.6" spans="1:15">
-      <c r="A43" s="12"/>
+    <row r="43" ht="20.25" spans="1:15">
+      <c r="A43" s="5"/>
       <c r="F43" s="2"/>
-      <c r="N43" s="14"/>
+      <c r="N43" s="11"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" ht="19.6" spans="1:15">
-      <c r="A44" s="12"/>
+    <row r="44" ht="20.25" spans="1:15">
+      <c r="A44" s="5"/>
       <c r="F44" s="2"/>
-      <c r="N44" s="14"/>
+      <c r="N44" s="11"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" ht="19.6" spans="1:15">
-      <c r="A45" s="12"/>
+    <row r="45" ht="20.25" spans="1:15">
+      <c r="A45" s="5"/>
       <c r="F45" s="2"/>
-      <c r="N45" s="14"/>
+      <c r="N45" s="11"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" ht="19.6" spans="1:15">
-      <c r="A46" s="12"/>
+    <row r="46" ht="20.25" spans="1:15">
+      <c r="A46" s="5"/>
       <c r="F46" s="2"/>
-      <c r="N46" s="14"/>
+      <c r="N46" s="11"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" ht="19.6" spans="1:15">
-      <c r="A47" s="12"/>
+    <row r="47" ht="20.25" spans="1:15">
+      <c r="A47" s="5"/>
       <c r="F47" s="2"/>
-      <c r="N47" s="14"/>
+      <c r="N47" s="11"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" ht="19.6" spans="1:15">
-      <c r="A48" s="12"/>
+    <row r="48" ht="20.25" spans="1:15">
+      <c r="A48" s="5"/>
       <c r="F48" s="2"/>
-      <c r="N48" s="14"/>
+      <c r="N48" s="11"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" ht="19.6" spans="1:15">
-      <c r="A49" s="12"/>
+    <row r="49" ht="20.25" spans="1:15">
+      <c r="A49" s="5"/>
       <c r="F49" s="2"/>
-      <c r="N49" s="14"/>
+      <c r="N49" s="11"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" ht="19.6" spans="1:15">
-      <c r="A50" s="12"/>
+    <row r="50" ht="20.25" spans="1:15">
+      <c r="A50" s="5"/>
       <c r="F50" s="2"/>
-      <c r="N50" s="14"/>
+      <c r="N50" s="11"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" ht="19.6" spans="1:15">
-      <c r="A51" s="12"/>
+    <row r="51" ht="20.25" spans="1:15">
+      <c r="A51" s="5"/>
       <c r="F51" s="2"/>
-      <c r="N51" s="14"/>
+      <c r="N51" s="11"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" ht="19.6" spans="1:15">
-      <c r="A52" s="12"/>
+    <row r="52" ht="20.25" spans="1:15">
+      <c r="A52" s="5"/>
       <c r="F52" s="2"/>
-      <c r="N52" s="14"/>
+      <c r="N52" s="11"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" ht="19.6" spans="1:15">
-      <c r="A53" s="12"/>
+    <row r="53" ht="20.25" spans="1:15">
+      <c r="A53" s="5"/>
       <c r="F53" s="2"/>
-      <c r="N53" s="14"/>
+      <c r="N53" s="11"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" ht="19.6" spans="1:15">
-      <c r="A54" s="12"/>
+    <row r="54" ht="20.25" spans="1:15">
+      <c r="A54" s="5"/>
       <c r="F54" s="2"/>
-      <c r="N54" s="14"/>
+      <c r="N54" s="11"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" ht="19.6" spans="1:1">
-      <c r="A55" s="12"/>
-    </row>
-    <row r="56" ht="19.6" spans="1:1">
-      <c r="A56" s="12"/>
-    </row>
-    <row r="57" ht="19.6" spans="1:1">
-      <c r="A57" s="12"/>
-    </row>
-    <row r="58" ht="19.6" spans="1:1">
-      <c r="A58" s="12"/>
-    </row>
-    <row r="59" ht="19.6" spans="1:1">
-      <c r="A59" s="12"/>
-    </row>
-    <row r="60" ht="19.6" spans="1:1">
-      <c r="A60" s="12"/>
-    </row>
-    <row r="61" ht="19.6" spans="1:1">
-      <c r="A61" s="12"/>
-    </row>
-    <row r="62" ht="19.6" spans="1:1">
-      <c r="A62" s="12"/>
-    </row>
-    <row r="63" ht="19.6" spans="1:1">
-      <c r="A63" s="12"/>
-    </row>
-    <row r="64" ht="19.6" spans="1:1">
-      <c r="A64" s="12"/>
-    </row>
-    <row r="65" ht="19.6" spans="1:1">
-      <c r="A65" s="12"/>
-    </row>
-    <row r="66" ht="19.6" spans="1:1">
-      <c r="A66" s="12"/>
-    </row>
-    <row r="67" ht="19.6" spans="1:1">
-      <c r="A67" s="12"/>
-    </row>
-    <row r="68" ht="19.6" spans="1:1">
-      <c r="A68" s="12"/>
-    </row>
-    <row r="69" ht="19.6" spans="1:1">
-      <c r="A69" s="12"/>
-    </row>
-    <row r="70" ht="19.6" spans="1:1">
-      <c r="A70" s="12"/>
-    </row>
-    <row r="71" ht="19.6" spans="1:1">
-      <c r="A71" s="12"/>
-    </row>
-    <row r="72" ht="19.6" spans="1:1">
-      <c r="A72" s="12"/>
-    </row>
-    <row r="73" ht="19.6" spans="1:1">
-      <c r="A73" s="12"/>
-    </row>
-    <row r="74" ht="19.6" spans="1:1">
-      <c r="A74" s="12"/>
-    </row>
-    <row r="75" ht="19.6" spans="1:1">
-      <c r="A75" s="12"/>
-    </row>
-    <row r="76" ht="19.6" spans="1:1">
-      <c r="A76" s="12"/>
-    </row>
-    <row r="77" ht="19.6" spans="1:1">
-      <c r="A77" s="12"/>
-    </row>
-    <row r="78" ht="19.6" spans="1:1">
-      <c r="A78" s="12"/>
-    </row>
-    <row r="79" ht="19.6" spans="1:1">
-      <c r="A79" s="12"/>
-    </row>
-    <row r="80" ht="19.6" spans="1:1">
-      <c r="A80" s="12"/>
-    </row>
-    <row r="81" ht="19.6" spans="1:1">
-      <c r="A81" s="12"/>
-    </row>
-    <row r="82" ht="19.6" spans="1:1">
-      <c r="A82" s="12"/>
-    </row>
-    <row r="83" ht="19.6" spans="1:1">
-      <c r="A83" s="12"/>
-    </row>
-    <row r="84" ht="19.6" spans="1:1">
-      <c r="A84" s="12"/>
-    </row>
-    <row r="85" ht="19.6" spans="1:1">
-      <c r="A85" s="12"/>
-    </row>
-    <row r="86" ht="19.6" spans="1:1">
-      <c r="A86" s="12"/>
-    </row>
-    <row r="87" ht="19.6" spans="1:1">
-      <c r="A87" s="12"/>
-    </row>
-    <row r="88" ht="19.6" spans="1:1">
-      <c r="A88" s="12"/>
-    </row>
-    <row r="89" ht="19.6" spans="1:1">
-      <c r="A89" s="12"/>
-    </row>
-    <row r="90" ht="19.6" spans="1:1">
-      <c r="A90" s="12"/>
-    </row>
-    <row r="91" ht="19.6" spans="1:1">
-      <c r="A91" s="12"/>
-    </row>
-    <row r="92" ht="19.6" spans="1:1">
-      <c r="A92" s="12"/>
-    </row>
-    <row r="93" ht="19.6" spans="1:1">
-      <c r="A93" s="12"/>
-    </row>
-    <row r="94" ht="19.6" spans="1:1">
-      <c r="A94" s="12"/>
-    </row>
-    <row r="95" ht="19.6" spans="1:1">
-      <c r="A95" s="12"/>
-    </row>
-    <row r="96" ht="19.6" spans="1:1">
-      <c r="A96" s="12"/>
-    </row>
-    <row r="97" ht="19.6" spans="1:1">
-      <c r="A97" s="12"/>
-    </row>
-    <row r="98" ht="19.6" spans="1:1">
-      <c r="A98" s="12"/>
-    </row>
-    <row r="99" ht="19.6" spans="1:1">
-      <c r="A99" s="12"/>
-    </row>
-    <row r="100" ht="19.6" spans="1:1">
-      <c r="A100" s="12"/>
-    </row>
-    <row r="101" ht="19.6" spans="1:1">
-      <c r="A101" s="12"/>
-    </row>
-    <row r="102" ht="19.6" spans="1:1">
-      <c r="A102" s="12"/>
-    </row>
-    <row r="103" ht="19.6" spans="1:1">
-      <c r="A103" s="12"/>
-    </row>
-    <row r="104" ht="19.6" spans="1:1">
-      <c r="A104" s="12"/>
-    </row>
-    <row r="105" ht="19.6" spans="1:1">
-      <c r="A105" s="12"/>
-    </row>
-    <row r="106" ht="19.6" spans="1:1">
-      <c r="A106" s="12"/>
-    </row>
-    <row r="107" ht="19.6" spans="1:1">
-      <c r="A107" s="12"/>
-    </row>
-    <row r="108" ht="19.6" spans="1:1">
-      <c r="A108" s="12"/>
-    </row>
-    <row r="109" ht="19.6" spans="1:1">
-      <c r="A109" s="12"/>
-    </row>
-    <row r="110" ht="19.6" spans="1:1">
-      <c r="A110" s="12"/>
-    </row>
-    <row r="111" ht="19.6" spans="1:1">
-      <c r="A111" s="12"/>
-    </row>
-    <row r="112" ht="19.6" spans="1:1">
-      <c r="A112" s="12"/>
-    </row>
-    <row r="113" ht="19.6" spans="1:1">
-      <c r="A113" s="12"/>
-    </row>
-    <row r="114" ht="19.6" spans="1:1">
-      <c r="A114" s="12"/>
-    </row>
-    <row r="115" ht="19.6" spans="1:1">
-      <c r="A115" s="12"/>
-    </row>
-    <row r="116" ht="19.6" spans="1:1">
-      <c r="A116" s="12"/>
-    </row>
-    <row r="117" ht="19.6" spans="1:1">
-      <c r="A117" s="12"/>
-    </row>
-    <row r="118" ht="19.6" spans="1:1">
-      <c r="A118" s="12"/>
-    </row>
-    <row r="119" ht="19.6" spans="1:1">
-      <c r="A119" s="12"/>
-    </row>
-    <row r="120" ht="19.6" spans="1:1">
-      <c r="A120" s="12"/>
-    </row>
-    <row r="121" ht="19.6" spans="1:1">
-      <c r="A121" s="12"/>
-    </row>
-    <row r="122" ht="19.6" spans="1:1">
-      <c r="A122" s="12"/>
-    </row>
-    <row r="123" ht="19.6" spans="1:1">
-      <c r="A123" s="12"/>
-    </row>
-    <row r="124" ht="19.6" spans="1:1">
-      <c r="A124" s="12"/>
-    </row>
-    <row r="125" ht="19.6" spans="1:1">
-      <c r="A125" s="12"/>
-    </row>
-    <row r="126" ht="19.6" spans="1:1">
-      <c r="A126" s="12"/>
-    </row>
-    <row r="127" ht="19.6" spans="1:1">
-      <c r="A127" s="12"/>
-    </row>
-    <row r="128" ht="19.6" spans="1:1">
-      <c r="A128" s="12"/>
-    </row>
-    <row r="129" ht="19.6" spans="1:1">
-      <c r="A129" s="12"/>
-    </row>
-    <row r="130" ht="19.6" spans="1:1">
-      <c r="A130" s="12"/>
-    </row>
-    <row r="131" ht="19.6" spans="1:1">
-      <c r="A131" s="12"/>
-    </row>
-    <row r="132" ht="19.6" spans="1:1">
-      <c r="A132" s="12"/>
-    </row>
-    <row r="133" ht="19.6" spans="1:1">
-      <c r="A133" s="12"/>
-    </row>
-    <row r="134" ht="19.6" spans="1:1">
-      <c r="A134" s="12"/>
-    </row>
-    <row r="135" ht="19.6" spans="1:1">
-      <c r="A135" s="12"/>
-    </row>
-    <row r="136" ht="19.6" spans="1:1">
-      <c r="A136" s="12"/>
-    </row>
-    <row r="137" ht="19.6" spans="1:1">
-      <c r="A137" s="12"/>
-    </row>
-    <row r="138" ht="19.6" spans="1:1">
-      <c r="A138" s="12"/>
-    </row>
-    <row r="139" ht="19.6" spans="1:1">
-      <c r="A139" s="12"/>
-    </row>
-    <row r="140" ht="19.6" spans="1:1">
-      <c r="A140" s="12"/>
-    </row>
-    <row r="141" ht="19.6" spans="1:1">
-      <c r="A141" s="12"/>
-    </row>
-    <row r="142" ht="19.6" spans="1:1">
-      <c r="A142" s="12"/>
-    </row>
-    <row r="143" ht="19.6" spans="1:1">
-      <c r="A143" s="12"/>
-    </row>
-    <row r="144" ht="19.6" spans="1:1">
-      <c r="A144" s="12"/>
-    </row>
-    <row r="145" ht="19.6" spans="1:1">
-      <c r="A145" s="12"/>
-    </row>
-    <row r="146" ht="19.6" spans="1:1">
-      <c r="A146" s="12"/>
-    </row>
-    <row r="147" ht="19.6" spans="1:1">
-      <c r="A147" s="12"/>
-    </row>
-    <row r="148" ht="19.6" spans="1:1">
-      <c r="A148" s="12"/>
-    </row>
-    <row r="149" ht="19.6" spans="1:1">
-      <c r="A149" s="12"/>
-    </row>
-    <row r="150" ht="19.6" spans="1:1">
-      <c r="A150" s="12"/>
-    </row>
-    <row r="151" ht="19.6" spans="1:1">
-      <c r="A151" s="12"/>
-    </row>
-    <row r="152" ht="19.6" spans="1:1">
-      <c r="A152" s="12"/>
-    </row>
-    <row r="153" ht="19.6" spans="1:1">
-      <c r="A153" s="12"/>
-    </row>
-    <row r="154" ht="19.6" spans="1:1">
-      <c r="A154" s="12"/>
-    </row>
-    <row r="155" ht="19.6" spans="1:1">
-      <c r="A155" s="12"/>
-    </row>
-    <row r="156" ht="19.6" spans="1:1">
-      <c r="A156" s="12"/>
-    </row>
-    <row r="157" ht="19.6" spans="1:1">
-      <c r="A157" s="12"/>
-    </row>
-    <row r="158" ht="19.6" spans="1:1">
-      <c r="A158" s="12"/>
-    </row>
-    <row r="159" ht="19.6" spans="1:1">
-      <c r="A159" s="12"/>
-    </row>
-    <row r="160" ht="19.6" spans="1:1">
-      <c r="A160" s="12"/>
-    </row>
-    <row r="161" ht="19.6" spans="1:1">
-      <c r="A161" s="12"/>
-    </row>
-    <row r="162" ht="19.6" spans="1:1">
-      <c r="A162" s="12"/>
-    </row>
-    <row r="163" ht="19.6" spans="1:1">
-      <c r="A163" s="12"/>
-    </row>
-    <row r="164" ht="19.6" spans="1:1">
-      <c r="A164" s="12"/>
-    </row>
-    <row r="165" ht="19.6" spans="1:1">
-      <c r="A165" s="12"/>
-    </row>
-    <row r="166" ht="19.6" spans="1:1">
-      <c r="A166" s="12"/>
-    </row>
-    <row r="167" ht="19.6" spans="1:1">
-      <c r="A167" s="12"/>
-    </row>
-    <row r="168" ht="19.6" spans="1:1">
-      <c r="A168" s="12"/>
-    </row>
-    <row r="169" ht="19.6" spans="1:1">
-      <c r="A169" s="12"/>
-    </row>
-    <row r="170" ht="19.6" spans="1:1">
-      <c r="A170" s="12"/>
-    </row>
-    <row r="171" ht="19.6" spans="1:1">
-      <c r="A171" s="12"/>
-    </row>
-    <row r="172" ht="19.6" spans="1:1">
-      <c r="A172" s="12"/>
-    </row>
-    <row r="173" ht="19.6" spans="1:1">
-      <c r="A173" s="12"/>
-    </row>
-    <row r="174" ht="19.6" spans="1:1">
-      <c r="A174" s="12"/>
-    </row>
-    <row r="175" ht="19.6" spans="1:1">
-      <c r="A175" s="12"/>
-    </row>
-    <row r="176" ht="19.6" spans="1:1">
-      <c r="A176" s="12"/>
-    </row>
-    <row r="177" ht="19.6" spans="1:1">
-      <c r="A177" s="12"/>
-    </row>
-    <row r="178" ht="19.6" spans="1:1">
-      <c r="A178" s="12"/>
-    </row>
-    <row r="179" ht="19.6" spans="1:1">
-      <c r="A179" s="12"/>
-    </row>
-    <row r="180" ht="19.6" spans="1:1">
-      <c r="A180" s="12"/>
-    </row>
-    <row r="181" ht="19.6" spans="1:1">
-      <c r="A181" s="12"/>
-    </row>
-    <row r="182" ht="19.6" spans="1:1">
-      <c r="A182" s="12"/>
-    </row>
-    <row r="183" ht="19.6" spans="1:1">
-      <c r="A183" s="12"/>
-    </row>
-    <row r="184" ht="19.6" spans="1:1">
-      <c r="A184" s="12"/>
-    </row>
-    <row r="185" ht="19.6" spans="1:1">
-      <c r="A185" s="12"/>
-    </row>
-    <row r="186" ht="19.6" spans="1:1">
-      <c r="A186" s="12"/>
-    </row>
-    <row r="187" ht="19.6" spans="1:1">
-      <c r="A187" s="12"/>
-    </row>
-    <row r="188" ht="19.6" spans="1:1">
-      <c r="A188" s="12"/>
-    </row>
-    <row r="189" ht="19.6" spans="1:1">
-      <c r="A189" s="12"/>
-    </row>
-    <row r="190" ht="19.6" spans="1:1">
-      <c r="A190" s="12"/>
-    </row>
-    <row r="191" ht="19.6" spans="1:1">
-      <c r="A191" s="12"/>
-    </row>
-    <row r="192" ht="19.6" spans="1:1">
-      <c r="A192" s="12"/>
-    </row>
-    <row r="193" ht="19.6" spans="1:1">
-      <c r="A193" s="12"/>
-    </row>
-    <row r="194" ht="19.6" spans="1:1">
-      <c r="A194" s="12"/>
-    </row>
-    <row r="195" ht="19.6" spans="1:1">
-      <c r="A195" s="12"/>
-    </row>
-    <row r="196" ht="19.6" spans="1:1">
-      <c r="A196" s="12"/>
-    </row>
-    <row r="197" ht="19.6" spans="1:1">
-      <c r="A197" s="12"/>
-    </row>
-    <row r="198" ht="19.6" spans="1:1">
-      <c r="A198" s="12"/>
-    </row>
-    <row r="199" ht="19.6" spans="1:1">
-      <c r="A199" s="12"/>
-    </row>
-    <row r="200" ht="19.6" spans="1:1">
-      <c r="A200" s="12"/>
-    </row>
-    <row r="201" ht="19.6" spans="1:1">
-      <c r="A201" s="12"/>
-    </row>
-    <row r="202" ht="19.6" spans="1:1">
-      <c r="A202" s="12"/>
-    </row>
-    <row r="203" ht="19.6" spans="1:1">
-      <c r="A203" s="12"/>
-    </row>
-    <row r="204" ht="19.6" spans="1:1">
-      <c r="A204" s="12"/>
-    </row>
-    <row r="205" ht="19.6" spans="1:1">
-      <c r="A205" s="12"/>
-    </row>
-    <row r="206" ht="19.6" spans="1:1">
-      <c r="A206" s="12"/>
-    </row>
-    <row r="207" ht="19.6" spans="1:1">
-      <c r="A207" s="12"/>
-    </row>
-    <row r="208" ht="19.6" spans="1:1">
-      <c r="A208" s="12"/>
-    </row>
-    <row r="209" ht="19.6" spans="1:1">
-      <c r="A209" s="12"/>
-    </row>
-    <row r="210" ht="19.6" spans="1:1">
-      <c r="A210" s="12"/>
-    </row>
-    <row r="211" ht="19.6" spans="1:1">
-      <c r="A211" s="12"/>
-    </row>
-    <row r="212" ht="19.6" spans="1:1">
-      <c r="A212" s="12"/>
-    </row>
-    <row r="213" ht="19.6" spans="1:1">
-      <c r="A213" s="12"/>
-    </row>
-    <row r="214" ht="19.6" spans="1:1">
-      <c r="A214" s="12"/>
-    </row>
-    <row r="215" ht="19.6" spans="1:1">
-      <c r="A215" s="12"/>
-    </row>
-    <row r="216" ht="19.6" spans="1:1">
-      <c r="A216" s="12"/>
-    </row>
-    <row r="217" ht="19.6" spans="1:1">
-      <c r="A217" s="12"/>
-    </row>
-    <row r="218" ht="19.6" spans="1:1">
-      <c r="A218" s="12"/>
-    </row>
-    <row r="219" ht="19.6" spans="1:1">
-      <c r="A219" s="12"/>
-    </row>
-    <row r="220" ht="19.6" spans="1:1">
-      <c r="A220" s="12"/>
-    </row>
-    <row r="221" ht="19.6" spans="1:1">
-      <c r="A221" s="12"/>
-    </row>
-    <row r="222" ht="19.6" spans="1:1">
-      <c r="A222" s="12"/>
-    </row>
-    <row r="223" ht="19.6" spans="1:1">
-      <c r="A223" s="12"/>
-    </row>
-    <row r="224" ht="19.6" spans="1:1">
-      <c r="A224" s="12"/>
-    </row>
-    <row r="225" ht="19.6" spans="1:1">
-      <c r="A225" s="12"/>
-    </row>
-    <row r="226" ht="19.6" spans="1:1">
-      <c r="A226" s="12"/>
-    </row>
-    <row r="227" ht="19.6" spans="1:1">
-      <c r="A227" s="12"/>
-    </row>
-    <row r="228" ht="19.6" spans="1:1">
-      <c r="A228" s="12"/>
-    </row>
-    <row r="229" ht="19.6" spans="1:1">
-      <c r="A229" s="12"/>
-    </row>
-    <row r="230" ht="19.6" spans="1:1">
-      <c r="A230" s="12"/>
-    </row>
-    <row r="231" ht="19.6" spans="1:1">
-      <c r="A231" s="12"/>
-    </row>
-    <row r="232" ht="19.6" spans="1:1">
-      <c r="A232" s="12"/>
-    </row>
-    <row r="233" ht="19.6" spans="1:1">
-      <c r="A233" s="12"/>
-    </row>
-    <row r="234" ht="19.6" spans="1:1">
-      <c r="A234" s="12"/>
-    </row>
-    <row r="235" ht="19.6" spans="1:1">
-      <c r="A235" s="12"/>
-    </row>
-    <row r="236" ht="19.6" spans="1:1">
-      <c r="A236" s="12"/>
-    </row>
-    <row r="237" ht="19.6" spans="1:1">
-      <c r="A237" s="12"/>
-    </row>
-    <row r="238" ht="19.6" spans="1:1">
-      <c r="A238" s="12"/>
-    </row>
-    <row r="239" ht="19.6" spans="1:1">
-      <c r="A239" s="12"/>
-    </row>
-    <row r="240" ht="19.6" spans="1:1">
-      <c r="A240" s="12"/>
-    </row>
-    <row r="241" ht="19.6" spans="1:1">
-      <c r="A241" s="12"/>
-    </row>
-    <row r="242" ht="19.6" spans="1:1">
-      <c r="A242" s="12"/>
-    </row>
-    <row r="243" ht="19.6" spans="1:1">
-      <c r="A243" s="12"/>
-    </row>
-    <row r="244" ht="19.6" spans="1:1">
-      <c r="A244" s="12"/>
-    </row>
-    <row r="245" ht="19.6" spans="1:1">
-      <c r="A245" s="12"/>
-    </row>
-    <row r="246" ht="19.6" spans="1:1">
-      <c r="A246" s="12"/>
-    </row>
-    <row r="247" ht="19.6" spans="1:1">
-      <c r="A247" s="12"/>
-    </row>
-    <row r="248" ht="19.6" spans="1:1">
-      <c r="A248" s="12"/>
-    </row>
-    <row r="249" ht="19.6" spans="1:1">
-      <c r="A249" s="12"/>
-    </row>
-    <row r="250" ht="19.6" spans="1:1">
-      <c r="A250" s="12"/>
-    </row>
-    <row r="251" ht="19.6" spans="1:1">
-      <c r="A251" s="12"/>
-    </row>
-    <row r="252" ht="19.6" spans="1:1">
-      <c r="A252" s="12"/>
-    </row>
-    <row r="253" ht="19.6" spans="1:1">
-      <c r="A253" s="12"/>
-    </row>
-    <row r="254" ht="19.6" spans="1:1">
-      <c r="A254" s="12"/>
-    </row>
-    <row r="255" ht="19.6" spans="1:1">
-      <c r="A255" s="12"/>
-    </row>
-    <row r="256" ht="19.6" spans="1:1">
-      <c r="A256" s="12"/>
-    </row>
-    <row r="257" ht="19.6" spans="1:1">
-      <c r="A257" s="12"/>
-    </row>
-    <row r="258" ht="19.6" spans="1:1">
-      <c r="A258" s="12"/>
-    </row>
-    <row r="259" ht="19.6" spans="1:1">
-      <c r="A259" s="12"/>
-    </row>
-    <row r="260" ht="19.6" spans="1:1">
-      <c r="A260" s="12"/>
-    </row>
-    <row r="261" ht="19.6" spans="1:1">
-      <c r="A261" s="12"/>
-    </row>
-    <row r="262" ht="19.6" spans="1:1">
-      <c r="A262" s="12"/>
-    </row>
-    <row r="263" ht="19.6" spans="1:1">
-      <c r="A263" s="12"/>
-    </row>
-    <row r="264" ht="19.6" spans="1:1">
-      <c r="A264" s="12"/>
-    </row>
-    <row r="265" ht="19.6" spans="1:1">
-      <c r="A265" s="12"/>
-    </row>
-    <row r="266" ht="19.6" spans="1:1">
-      <c r="A266" s="12"/>
-    </row>
-    <row r="267" ht="19.6" spans="1:1">
-      <c r="A267" s="12"/>
-    </row>
-    <row r="268" ht="19.6" spans="1:1">
-      <c r="A268" s="12"/>
-    </row>
-    <row r="269" ht="19.6" spans="1:1">
-      <c r="A269" s="12"/>
-    </row>
-    <row r="270" ht="19.6" spans="1:1">
-      <c r="A270" s="12"/>
-    </row>
-    <row r="271" ht="19.6" spans="1:1">
-      <c r="A271" s="12"/>
-    </row>
-    <row r="272" ht="19.6" spans="1:1">
-      <c r="A272" s="12"/>
-    </row>
-    <row r="273" ht="19.6" spans="1:1">
-      <c r="A273" s="12"/>
-    </row>
-    <row r="274" ht="19.6" spans="1:1">
-      <c r="A274" s="12"/>
-    </row>
-    <row r="275" ht="19.6" spans="1:1">
-      <c r="A275" s="12"/>
-    </row>
-    <row r="276" ht="19.6" spans="1:1">
-      <c r="A276" s="12"/>
-    </row>
-    <row r="277" ht="19.6" spans="1:1">
-      <c r="A277" s="12"/>
-    </row>
-    <row r="278" ht="19.6" spans="1:1">
-      <c r="A278" s="12"/>
-    </row>
-    <row r="279" ht="19.6" spans="1:1">
-      <c r="A279" s="12"/>
-    </row>
-    <row r="280" ht="19.6" spans="1:1">
-      <c r="A280" s="12"/>
-    </row>
-    <row r="281" ht="19.6" spans="1:1">
-      <c r="A281" s="12"/>
-    </row>
-    <row r="282" ht="19.6" spans="1:1">
-      <c r="A282" s="12"/>
-    </row>
-    <row r="283" ht="19.6" spans="1:1">
-      <c r="A283" s="12"/>
-    </row>
-    <row r="284" ht="19.6" spans="1:1">
-      <c r="A284" s="12"/>
-    </row>
-    <row r="285" ht="19.6" spans="1:1">
-      <c r="A285" s="12"/>
-    </row>
-    <row r="286" ht="19.6" spans="1:1">
-      <c r="A286" s="12"/>
-    </row>
-    <row r="287" ht="19.6" spans="1:1">
-      <c r="A287" s="12"/>
-    </row>
-    <row r="288" ht="19.6" spans="1:1">
-      <c r="A288" s="12"/>
-    </row>
-    <row r="289" ht="19.6" spans="1:1">
-      <c r="A289" s="12"/>
-    </row>
-    <row r="290" ht="19.6" spans="1:1">
-      <c r="A290" s="12"/>
-    </row>
-    <row r="291" ht="19.6" spans="1:1">
-      <c r="A291" s="12"/>
-    </row>
-    <row r="292" ht="19.6" spans="1:1">
-      <c r="A292" s="12"/>
-    </row>
-    <row r="293" ht="19.6" spans="1:1">
-      <c r="A293" s="12"/>
-    </row>
-    <row r="294" ht="19.6" spans="1:1">
-      <c r="A294" s="12"/>
-    </row>
-    <row r="295" ht="19.6" spans="1:1">
-      <c r="A295" s="12"/>
-    </row>
-    <row r="296" ht="19.6" spans="1:1">
-      <c r="A296" s="12"/>
-    </row>
-    <row r="297" ht="19.6" spans="1:1">
-      <c r="A297" s="12"/>
-    </row>
-    <row r="298" ht="19.6" spans="1:1">
-      <c r="A298" s="12"/>
-    </row>
-    <row r="299" ht="19.6" spans="1:1">
-      <c r="A299" s="12"/>
-    </row>
-    <row r="300" ht="19.6" spans="1:1">
-      <c r="A300" s="12"/>
-    </row>
-    <row r="301" ht="19.6" spans="1:1">
-      <c r="A301" s="12"/>
-    </row>
-    <row r="302" ht="19.6" spans="1:1">
-      <c r="A302" s="12"/>
-    </row>
-    <row r="303" ht="19.6" spans="1:1">
-      <c r="A303" s="12"/>
-    </row>
-    <row r="304" ht="19.6" spans="1:1">
-      <c r="A304" s="12"/>
-    </row>
-    <row r="305" ht="19.6" spans="1:1">
-      <c r="A305" s="12"/>
-    </row>
-    <row r="306" ht="19.6" spans="1:1">
-      <c r="A306" s="12"/>
-    </row>
-    <row r="307" ht="19.6" spans="1:1">
-      <c r="A307" s="12"/>
-    </row>
-    <row r="308" ht="19.6" spans="1:1">
-      <c r="A308" s="12"/>
-    </row>
-    <row r="309" ht="19.6" spans="1:1">
-      <c r="A309" s="12"/>
-    </row>
-    <row r="310" ht="19.6" spans="1:1">
-      <c r="A310" s="12"/>
-    </row>
-    <row r="311" ht="19.6" spans="1:1">
-      <c r="A311" s="12"/>
-    </row>
-    <row r="312" ht="19.6" spans="1:1">
-      <c r="A312" s="12"/>
-    </row>
-    <row r="313" ht="19.6" spans="1:1">
-      <c r="A313" s="12"/>
-    </row>
-    <row r="314" ht="19.6" spans="1:1">
-      <c r="A314" s="12"/>
-    </row>
-    <row r="315" ht="19.6" spans="1:1">
-      <c r="A315" s="12"/>
-    </row>
-    <row r="316" ht="19.6" spans="1:1">
-      <c r="A316" s="12"/>
-    </row>
-    <row r="317" ht="19.6" spans="1:1">
-      <c r="A317" s="12"/>
-    </row>
-    <row r="318" ht="19.6" spans="1:1">
-      <c r="A318" s="12"/>
-    </row>
-    <row r="319" ht="19.6" spans="1:1">
-      <c r="A319" s="12"/>
-    </row>
-    <row r="320" ht="19.6" spans="1:1">
-      <c r="A320" s="12"/>
-    </row>
-    <row r="321" ht="19.6" spans="1:1">
-      <c r="A321" s="12"/>
-    </row>
-    <row r="322" ht="19.6" spans="1:1">
-      <c r="A322" s="12"/>
-    </row>
-    <row r="323" ht="19.6" spans="1:1">
-      <c r="A323" s="12"/>
-    </row>
-    <row r="324" ht="19.6" spans="1:1">
-      <c r="A324" s="12"/>
-    </row>
-    <row r="325" ht="19.6" spans="1:1">
-      <c r="A325" s="12"/>
-    </row>
-    <row r="326" ht="19.6" spans="1:1">
-      <c r="A326" s="12"/>
-    </row>
-    <row r="327" ht="19.6" spans="1:1">
-      <c r="A327" s="12"/>
-    </row>
-    <row r="328" ht="19.6" spans="1:1">
-      <c r="A328" s="12"/>
-    </row>
-    <row r="329" ht="19.6" spans="1:1">
-      <c r="A329" s="12"/>
-    </row>
-    <row r="330" ht="19.6" spans="1:1">
-      <c r="A330" s="12"/>
-    </row>
-    <row r="331" ht="19.6" spans="1:1">
-      <c r="A331" s="12"/>
-    </row>
-    <row r="332" ht="19.6" spans="1:1">
-      <c r="A332" s="12"/>
-    </row>
-    <row r="333" ht="19.6" spans="1:1">
-      <c r="A333" s="12"/>
-    </row>
-    <row r="334" ht="19.6" spans="1:1">
-      <c r="A334" s="12"/>
-    </row>
-    <row r="335" ht="19.6" spans="1:1">
-      <c r="A335" s="12"/>
-    </row>
-    <row r="336" ht="19.6" spans="1:1">
-      <c r="A336" s="12"/>
-    </row>
-    <row r="337" ht="19.6" spans="1:1">
-      <c r="A337" s="12"/>
-    </row>
-    <row r="338" ht="19.6" spans="1:1">
-      <c r="A338" s="12"/>
-    </row>
-    <row r="339" ht="19.6" spans="1:1">
-      <c r="A339" s="12"/>
-    </row>
-    <row r="340" ht="19.6" spans="1:1">
-      <c r="A340" s="12"/>
-    </row>
-    <row r="341" ht="19.6" spans="1:1">
-      <c r="A341" s="12"/>
-    </row>
-    <row r="342" ht="19.6" spans="1:1">
-      <c r="A342" s="12"/>
-    </row>
-    <row r="343" ht="19.6" spans="1:1">
-      <c r="A343" s="12"/>
-    </row>
-    <row r="344" ht="19.6" spans="1:1">
-      <c r="A344" s="12"/>
-    </row>
-    <row r="345" ht="19.6" spans="1:1">
-      <c r="A345" s="12"/>
-    </row>
-    <row r="346" ht="19.6" spans="1:1">
-      <c r="A346" s="12"/>
-    </row>
-    <row r="347" ht="19.6" spans="1:1">
-      <c r="A347" s="12"/>
-    </row>
-    <row r="348" ht="19.6" spans="1:1">
-      <c r="A348" s="12"/>
-    </row>
-    <row r="349" ht="19.6" spans="1:1">
-      <c r="A349" s="12"/>
-    </row>
-    <row r="350" ht="19.6" spans="1:1">
-      <c r="A350" s="12"/>
-    </row>
-    <row r="351" ht="19.6" spans="1:1">
-      <c r="A351" s="12"/>
-    </row>
-    <row r="352" ht="19.6" spans="1:1">
-      <c r="A352" s="12"/>
-    </row>
-    <row r="353" ht="19.6" spans="1:1">
-      <c r="A353" s="12"/>
-    </row>
-    <row r="354" ht="19.6" spans="1:1">
-      <c r="A354" s="12"/>
-    </row>
-    <row r="355" ht="19.6" spans="1:1">
-      <c r="A355" s="12"/>
-    </row>
-    <row r="356" ht="19.6" spans="1:1">
-      <c r="A356" s="12"/>
-    </row>
-    <row r="357" ht="19.6" spans="1:1">
-      <c r="A357" s="12"/>
-    </row>
-    <row r="358" ht="19.6" spans="1:1">
-      <c r="A358" s="12"/>
-    </row>
-    <row r="359" ht="19.6" spans="1:1">
-      <c r="A359" s="12"/>
-    </row>
-    <row r="360" ht="19.6" spans="1:1">
-      <c r="A360" s="12"/>
-    </row>
-    <row r="361" ht="19.6" spans="1:1">
-      <c r="A361" s="12"/>
-    </row>
-    <row r="362" ht="19.6" spans="1:1">
-      <c r="A362" s="12"/>
-    </row>
-    <row r="363" ht="19.6" spans="1:1">
-      <c r="A363" s="12"/>
-    </row>
-    <row r="364" ht="19.6" spans="1:1">
-      <c r="A364" s="12"/>
-    </row>
-    <row r="365" ht="19.6" spans="1:1">
-      <c r="A365" s="12"/>
-    </row>
-    <row r="366" ht="19.6" spans="1:1">
-      <c r="A366" s="12"/>
+    <row r="55" ht="20.25" spans="1:15">
+      <c r="A55" s="5"/>
+    </row>
+    <row r="56" ht="20.25" spans="1:15">
+      <c r="A56" s="5"/>
+    </row>
+    <row r="57" ht="20.25" spans="1:15">
+      <c r="A57" s="5"/>
+    </row>
+    <row r="58" ht="20.25" spans="1:15">
+      <c r="A58" s="5"/>
+    </row>
+    <row r="59" ht="20.25" spans="1:15">
+      <c r="A59" s="5"/>
+    </row>
+    <row r="60" ht="20.25" spans="1:15">
+      <c r="A60" s="5"/>
+    </row>
+    <row r="61" ht="20.25" spans="1:15">
+      <c r="A61" s="5"/>
+    </row>
+    <row r="62" ht="20.25" spans="1:15">
+      <c r="A62" s="5"/>
+    </row>
+    <row r="63" ht="20.25" spans="1:15">
+      <c r="A63" s="5"/>
+    </row>
+    <row r="64" ht="20.25" spans="1:15">
+      <c r="A64" s="5"/>
+    </row>
+    <row r="65" ht="20.25" spans="1:1">
+      <c r="A65" s="5"/>
+    </row>
+    <row r="66" ht="20.25" spans="1:1">
+      <c r="A66" s="5"/>
+    </row>
+    <row r="67" ht="20.25" spans="1:1">
+      <c r="A67" s="5"/>
+    </row>
+    <row r="68" ht="20.25" spans="1:1">
+      <c r="A68" s="5"/>
+    </row>
+    <row r="69" ht="20.25" spans="1:1">
+      <c r="A69" s="5"/>
+    </row>
+    <row r="70" ht="20.25" spans="1:1">
+      <c r="A70" s="5"/>
+    </row>
+    <row r="71" ht="20.25" spans="1:1">
+      <c r="A71" s="5"/>
+    </row>
+    <row r="72" ht="20.25" spans="1:1">
+      <c r="A72" s="5"/>
+    </row>
+    <row r="73" ht="20.25" spans="1:1">
+      <c r="A73" s="5"/>
+    </row>
+    <row r="74" ht="20.25" spans="1:1">
+      <c r="A74" s="5"/>
+    </row>
+    <row r="75" ht="20.25" spans="1:1">
+      <c r="A75" s="5"/>
+    </row>
+    <row r="76" ht="20.25" spans="1:1">
+      <c r="A76" s="5"/>
+    </row>
+    <row r="77" ht="20.25" spans="1:1">
+      <c r="A77" s="5"/>
+    </row>
+    <row r="78" ht="20.25" spans="1:1">
+      <c r="A78" s="5"/>
+    </row>
+    <row r="79" ht="20.25" spans="1:1">
+      <c r="A79" s="5"/>
+    </row>
+    <row r="80" ht="20.25" spans="1:1">
+      <c r="A80" s="5"/>
+    </row>
+    <row r="81" ht="20.25" spans="1:1">
+      <c r="A81" s="5"/>
+    </row>
+    <row r="82" ht="20.25" spans="1:1">
+      <c r="A82" s="5"/>
+    </row>
+    <row r="83" ht="20.25" spans="1:1">
+      <c r="A83" s="5"/>
+    </row>
+    <row r="84" ht="20.25" spans="1:1">
+      <c r="A84" s="5"/>
+    </row>
+    <row r="85" ht="20.25" spans="1:1">
+      <c r="A85" s="5"/>
+    </row>
+    <row r="86" ht="20.25" spans="1:1">
+      <c r="A86" s="5"/>
+    </row>
+    <row r="87" ht="20.25" spans="1:1">
+      <c r="A87" s="5"/>
+    </row>
+    <row r="88" ht="20.25" spans="1:1">
+      <c r="A88" s="5"/>
+    </row>
+    <row r="89" ht="20.25" spans="1:1">
+      <c r="A89" s="5"/>
+    </row>
+    <row r="90" ht="20.25" spans="1:1">
+      <c r="A90" s="5"/>
+    </row>
+    <row r="91" ht="20.25" spans="1:1">
+      <c r="A91" s="5"/>
+    </row>
+    <row r="92" ht="20.25" spans="1:1">
+      <c r="A92" s="5"/>
+    </row>
+    <row r="93" ht="20.25" spans="1:1">
+      <c r="A93" s="5"/>
+    </row>
+    <row r="94" ht="20.25" spans="1:1">
+      <c r="A94" s="5"/>
+    </row>
+    <row r="95" ht="20.25" spans="1:1">
+      <c r="A95" s="5"/>
+    </row>
+    <row r="96" ht="20.25" spans="1:1">
+      <c r="A96" s="5"/>
+    </row>
+    <row r="97" ht="20.25" spans="1:1">
+      <c r="A97" s="5"/>
+    </row>
+    <row r="98" ht="20.25" spans="1:1">
+      <c r="A98" s="5"/>
+    </row>
+    <row r="99" ht="20.25" spans="1:1">
+      <c r="A99" s="5"/>
+    </row>
+    <row r="100" ht="20.25" spans="1:1">
+      <c r="A100" s="5"/>
+    </row>
+    <row r="101" ht="20.25" spans="1:1">
+      <c r="A101" s="5"/>
+    </row>
+    <row r="102" ht="20.25" spans="1:1">
+      <c r="A102" s="5"/>
+    </row>
+    <row r="103" ht="20.25" spans="1:1">
+      <c r="A103" s="5"/>
+    </row>
+    <row r="104" ht="20.25" spans="1:1">
+      <c r="A104" s="5"/>
+    </row>
+    <row r="105" ht="20.25" spans="1:1">
+      <c r="A105" s="5"/>
+    </row>
+    <row r="106" ht="20.25" spans="1:1">
+      <c r="A106" s="5"/>
+    </row>
+    <row r="107" ht="20.25" spans="1:1">
+      <c r="A107" s="5"/>
+    </row>
+    <row r="108" ht="20.25" spans="1:1">
+      <c r="A108" s="5"/>
+    </row>
+    <row r="109" ht="20.25" spans="1:1">
+      <c r="A109" s="5"/>
+    </row>
+    <row r="110" ht="20.25" spans="1:1">
+      <c r="A110" s="5"/>
+    </row>
+    <row r="111" ht="20.25" spans="1:1">
+      <c r="A111" s="5"/>
+    </row>
+    <row r="112" ht="20.25" spans="1:1">
+      <c r="A112" s="5"/>
+    </row>
+    <row r="113" ht="20.25" spans="1:1">
+      <c r="A113" s="5"/>
+    </row>
+    <row r="114" ht="20.25" spans="1:1">
+      <c r="A114" s="5"/>
+    </row>
+    <row r="115" ht="20.25" spans="1:1">
+      <c r="A115" s="5"/>
+    </row>
+    <row r="116" ht="20.25" spans="1:1">
+      <c r="A116" s="5"/>
+    </row>
+    <row r="117" ht="20.25" spans="1:1">
+      <c r="A117" s="5"/>
+    </row>
+    <row r="118" ht="20.25" spans="1:1">
+      <c r="A118" s="5"/>
+    </row>
+    <row r="119" ht="20.25" spans="1:1">
+      <c r="A119" s="5"/>
+    </row>
+    <row r="120" ht="20.25" spans="1:1">
+      <c r="A120" s="5"/>
+    </row>
+    <row r="121" ht="20.25" spans="1:1">
+      <c r="A121" s="5"/>
+    </row>
+    <row r="122" ht="20.25" spans="1:1">
+      <c r="A122" s="5"/>
+    </row>
+    <row r="123" ht="20.25" spans="1:1">
+      <c r="A123" s="5"/>
+    </row>
+    <row r="124" ht="20.25" spans="1:1">
+      <c r="A124" s="5"/>
+    </row>
+    <row r="125" ht="20.25" spans="1:1">
+      <c r="A125" s="5"/>
+    </row>
+    <row r="126" ht="20.25" spans="1:1">
+      <c r="A126" s="5"/>
+    </row>
+    <row r="127" ht="20.25" spans="1:1">
+      <c r="A127" s="5"/>
+    </row>
+    <row r="128" ht="20.25" spans="1:1">
+      <c r="A128" s="5"/>
+    </row>
+    <row r="129" ht="20.25" spans="1:1">
+      <c r="A129" s="5"/>
+    </row>
+    <row r="130" ht="20.25" spans="1:1">
+      <c r="A130" s="5"/>
+    </row>
+    <row r="131" ht="20.25" spans="1:1">
+      <c r="A131" s="5"/>
+    </row>
+    <row r="132" ht="20.25" spans="1:1">
+      <c r="A132" s="5"/>
+    </row>
+    <row r="133" ht="20.25" spans="1:1">
+      <c r="A133" s="5"/>
+    </row>
+    <row r="134" ht="20.25" spans="1:1">
+      <c r="A134" s="5"/>
+    </row>
+    <row r="135" ht="20.25" spans="1:1">
+      <c r="A135" s="5"/>
+    </row>
+    <row r="136" ht="20.25" spans="1:1">
+      <c r="A136" s="5"/>
+    </row>
+    <row r="137" ht="20.25" spans="1:1">
+      <c r="A137" s="5"/>
+    </row>
+    <row r="138" ht="20.25" spans="1:1">
+      <c r="A138" s="5"/>
+    </row>
+    <row r="139" ht="20.25" spans="1:1">
+      <c r="A139" s="5"/>
+    </row>
+    <row r="140" ht="20.25" spans="1:1">
+      <c r="A140" s="5"/>
+    </row>
+    <row r="141" ht="20.25" spans="1:1">
+      <c r="A141" s="5"/>
+    </row>
+    <row r="142" ht="20.25" spans="1:1">
+      <c r="A142" s="5"/>
+    </row>
+    <row r="143" ht="20.25" spans="1:1">
+      <c r="A143" s="5"/>
+    </row>
+    <row r="144" ht="20.25" spans="1:1">
+      <c r="A144" s="5"/>
+    </row>
+    <row r="145" ht="20.25" spans="1:1">
+      <c r="A145" s="5"/>
+    </row>
+    <row r="146" ht="20.25" spans="1:1">
+      <c r="A146" s="5"/>
+    </row>
+    <row r="147" ht="20.25" spans="1:1">
+      <c r="A147" s="5"/>
+    </row>
+    <row r="148" ht="20.25" spans="1:1">
+      <c r="A148" s="5"/>
+    </row>
+    <row r="149" ht="20.25" spans="1:1">
+      <c r="A149" s="5"/>
+    </row>
+    <row r="150" ht="20.25" spans="1:1">
+      <c r="A150" s="5"/>
+    </row>
+    <row r="151" ht="20.25" spans="1:1">
+      <c r="A151" s="5"/>
+    </row>
+    <row r="152" ht="20.25" spans="1:1">
+      <c r="A152" s="5"/>
+    </row>
+    <row r="153" ht="20.25" spans="1:1">
+      <c r="A153" s="5"/>
+    </row>
+    <row r="154" ht="20.25" spans="1:1">
+      <c r="A154" s="5"/>
+    </row>
+    <row r="155" ht="20.25" spans="1:1">
+      <c r="A155" s="5"/>
+    </row>
+    <row r="156" ht="20.25" spans="1:1">
+      <c r="A156" s="5"/>
+    </row>
+    <row r="157" ht="20.25" spans="1:1">
+      <c r="A157" s="5"/>
+    </row>
+    <row r="158" ht="20.25" spans="1:1">
+      <c r="A158" s="5"/>
+    </row>
+    <row r="159" ht="20.25" spans="1:1">
+      <c r="A159" s="5"/>
+    </row>
+    <row r="160" ht="20.25" spans="1:1">
+      <c r="A160" s="5"/>
+    </row>
+    <row r="161" ht="20.25" spans="1:1">
+      <c r="A161" s="5"/>
+    </row>
+    <row r="162" ht="20.25" spans="1:1">
+      <c r="A162" s="5"/>
+    </row>
+    <row r="163" ht="20.25" spans="1:1">
+      <c r="A163" s="5"/>
+    </row>
+    <row r="164" ht="20.25" spans="1:1">
+      <c r="A164" s="5"/>
+    </row>
+    <row r="165" ht="20.25" spans="1:1">
+      <c r="A165" s="5"/>
+    </row>
+    <row r="166" ht="20.25" spans="1:1">
+      <c r="A166" s="5"/>
+    </row>
+    <row r="167" ht="20.25" spans="1:1">
+      <c r="A167" s="5"/>
+    </row>
+    <row r="168" ht="20.25" spans="1:1">
+      <c r="A168" s="5"/>
+    </row>
+    <row r="169" ht="20.25" spans="1:1">
+      <c r="A169" s="5"/>
+    </row>
+    <row r="170" ht="20.25" spans="1:1">
+      <c r="A170" s="5"/>
+    </row>
+    <row r="171" ht="20.25" spans="1:1">
+      <c r="A171" s="5"/>
+    </row>
+    <row r="172" ht="20.25" spans="1:1">
+      <c r="A172" s="5"/>
+    </row>
+    <row r="173" ht="20.25" spans="1:1">
+      <c r="A173" s="5"/>
+    </row>
+    <row r="174" ht="20.25" spans="1:1">
+      <c r="A174" s="5"/>
+    </row>
+    <row r="175" ht="20.25" spans="1:1">
+      <c r="A175" s="5"/>
+    </row>
+    <row r="176" ht="20.25" spans="1:1">
+      <c r="A176" s="5"/>
+    </row>
+    <row r="177" ht="20.25" spans="1:1">
+      <c r="A177" s="5"/>
+    </row>
+    <row r="178" ht="20.25" spans="1:1">
+      <c r="A178" s="5"/>
+    </row>
+    <row r="179" ht="20.25" spans="1:1">
+      <c r="A179" s="5"/>
+    </row>
+    <row r="180" ht="20.25" spans="1:1">
+      <c r="A180" s="5"/>
+    </row>
+    <row r="181" ht="20.25" spans="1:1">
+      <c r="A181" s="5"/>
+    </row>
+    <row r="182" ht="20.25" spans="1:1">
+      <c r="A182" s="5"/>
+    </row>
+    <row r="183" ht="20.25" spans="1:1">
+      <c r="A183" s="5"/>
+    </row>
+    <row r="184" ht="20.25" spans="1:1">
+      <c r="A184" s="5"/>
+    </row>
+    <row r="185" ht="20.25" spans="1:1">
+      <c r="A185" s="5"/>
+    </row>
+    <row r="186" ht="20.25" spans="1:1">
+      <c r="A186" s="5"/>
+    </row>
+    <row r="187" ht="20.25" spans="1:1">
+      <c r="A187" s="5"/>
+    </row>
+    <row r="188" ht="20.25" spans="1:1">
+      <c r="A188" s="5"/>
+    </row>
+    <row r="189" ht="20.25" spans="1:1">
+      <c r="A189" s="5"/>
+    </row>
+    <row r="190" ht="20.25" spans="1:1">
+      <c r="A190" s="5"/>
+    </row>
+    <row r="191" ht="20.25" spans="1:1">
+      <c r="A191" s="5"/>
+    </row>
+    <row r="192" ht="20.25" spans="1:1">
+      <c r="A192" s="5"/>
+    </row>
+    <row r="193" ht="20.25" spans="1:1">
+      <c r="A193" s="5"/>
+    </row>
+    <row r="194" ht="20.25" spans="1:1">
+      <c r="A194" s="5"/>
+    </row>
+    <row r="195" ht="20.25" spans="1:1">
+      <c r="A195" s="5"/>
+    </row>
+    <row r="196" ht="20.25" spans="1:1">
+      <c r="A196" s="5"/>
+    </row>
+    <row r="197" ht="20.25" spans="1:1">
+      <c r="A197" s="5"/>
+    </row>
+    <row r="198" ht="20.25" spans="1:1">
+      <c r="A198" s="5"/>
+    </row>
+    <row r="199" ht="20.25" spans="1:1">
+      <c r="A199" s="5"/>
+    </row>
+    <row r="200" ht="20.25" spans="1:1">
+      <c r="A200" s="5"/>
+    </row>
+    <row r="201" ht="20.25" spans="1:1">
+      <c r="A201" s="5"/>
+    </row>
+    <row r="202" ht="20.25" spans="1:1">
+      <c r="A202" s="5"/>
+    </row>
+    <row r="203" ht="20.25" spans="1:1">
+      <c r="A203" s="5"/>
+    </row>
+    <row r="204" ht="20.25" spans="1:1">
+      <c r="A204" s="5"/>
+    </row>
+    <row r="205" ht="20.25" spans="1:1">
+      <c r="A205" s="5"/>
+    </row>
+    <row r="206" ht="20.25" spans="1:1">
+      <c r="A206" s="5"/>
+    </row>
+    <row r="207" ht="20.25" spans="1:1">
+      <c r="A207" s="5"/>
+    </row>
+    <row r="208" ht="20.25" spans="1:1">
+      <c r="A208" s="5"/>
+    </row>
+    <row r="209" ht="20.25" spans="1:1">
+      <c r="A209" s="5"/>
+    </row>
+    <row r="210" ht="20.25" spans="1:1">
+      <c r="A210" s="5"/>
+    </row>
+    <row r="211" ht="20.25" spans="1:1">
+      <c r="A211" s="5"/>
+    </row>
+    <row r="212" ht="20.25" spans="1:1">
+      <c r="A212" s="5"/>
+    </row>
+    <row r="213" ht="20.25" spans="1:1">
+      <c r="A213" s="5"/>
+    </row>
+    <row r="214" ht="20.25" spans="1:1">
+      <c r="A214" s="5"/>
+    </row>
+    <row r="215" ht="20.25" spans="1:1">
+      <c r="A215" s="5"/>
+    </row>
+    <row r="216" ht="20.25" spans="1:1">
+      <c r="A216" s="5"/>
+    </row>
+    <row r="217" ht="20.25" spans="1:1">
+      <c r="A217" s="5"/>
+    </row>
+    <row r="218" ht="20.25" spans="1:1">
+      <c r="A218" s="5"/>
+    </row>
+    <row r="219" ht="20.25" spans="1:1">
+      <c r="A219" s="5"/>
+    </row>
+    <row r="220" ht="20.25" spans="1:1">
+      <c r="A220" s="5"/>
+    </row>
+    <row r="221" ht="20.25" spans="1:1">
+      <c r="A221" s="5"/>
+    </row>
+    <row r="222" ht="20.25" spans="1:1">
+      <c r="A222" s="5"/>
+    </row>
+    <row r="223" ht="20.25" spans="1:1">
+      <c r="A223" s="5"/>
+    </row>
+    <row r="224" ht="20.25" spans="1:1">
+      <c r="A224" s="5"/>
+    </row>
+    <row r="225" ht="20.25" spans="1:1">
+      <c r="A225" s="5"/>
+    </row>
+    <row r="226" ht="20.25" spans="1:1">
+      <c r="A226" s="5"/>
+    </row>
+    <row r="227" ht="20.25" spans="1:1">
+      <c r="A227" s="5"/>
+    </row>
+    <row r="228" ht="20.25" spans="1:1">
+      <c r="A228" s="5"/>
+    </row>
+    <row r="229" ht="20.25" spans="1:1">
+      <c r="A229" s="5"/>
+    </row>
+    <row r="230" ht="20.25" spans="1:1">
+      <c r="A230" s="5"/>
+    </row>
+    <row r="231" ht="20.25" spans="1:1">
+      <c r="A231" s="5"/>
+    </row>
+    <row r="232" ht="20.25" spans="1:1">
+      <c r="A232" s="5"/>
+    </row>
+    <row r="233" ht="20.25" spans="1:1">
+      <c r="A233" s="5"/>
+    </row>
+    <row r="234" ht="20.25" spans="1:1">
+      <c r="A234" s="5"/>
+    </row>
+    <row r="235" ht="20.25" spans="1:1">
+      <c r="A235" s="5"/>
+    </row>
+    <row r="236" ht="20.25" spans="1:1">
+      <c r="A236" s="5"/>
+    </row>
+    <row r="237" ht="20.25" spans="1:1">
+      <c r="A237" s="5"/>
+    </row>
+    <row r="238" ht="20.25" spans="1:1">
+      <c r="A238" s="5"/>
+    </row>
+    <row r="239" ht="20.25" spans="1:1">
+      <c r="A239" s="5"/>
+    </row>
+    <row r="240" ht="20.25" spans="1:1">
+      <c r="A240" s="5"/>
+    </row>
+    <row r="241" ht="20.25" spans="1:1">
+      <c r="A241" s="5"/>
+    </row>
+    <row r="242" ht="20.25" spans="1:1">
+      <c r="A242" s="5"/>
+    </row>
+    <row r="243" ht="20.25" spans="1:1">
+      <c r="A243" s="5"/>
+    </row>
+    <row r="244" ht="20.25" spans="1:1">
+      <c r="A244" s="5"/>
+    </row>
+    <row r="245" ht="20.25" spans="1:1">
+      <c r="A245" s="5"/>
+    </row>
+    <row r="246" ht="20.25" spans="1:1">
+      <c r="A246" s="5"/>
+    </row>
+    <row r="247" ht="20.25" spans="1:1">
+      <c r="A247" s="5"/>
+    </row>
+    <row r="248" ht="20.25" spans="1:1">
+      <c r="A248" s="5"/>
+    </row>
+    <row r="249" ht="20.25" spans="1:1">
+      <c r="A249" s="5"/>
+    </row>
+    <row r="250" ht="20.25" spans="1:1">
+      <c r="A250" s="5"/>
+    </row>
+    <row r="251" ht="20.25" spans="1:1">
+      <c r="A251" s="5"/>
+    </row>
+    <row r="252" ht="20.25" spans="1:1">
+      <c r="A252" s="5"/>
+    </row>
+    <row r="253" ht="20.25" spans="1:1">
+      <c r="A253" s="5"/>
+    </row>
+    <row r="254" ht="20.25" spans="1:1">
+      <c r="A254" s="5"/>
+    </row>
+    <row r="255" ht="20.25" spans="1:1">
+      <c r="A255" s="5"/>
+    </row>
+    <row r="256" ht="20.25" spans="1:1">
+      <c r="A256" s="5"/>
+    </row>
+    <row r="257" ht="20.25" spans="1:1">
+      <c r="A257" s="5"/>
+    </row>
+    <row r="258" ht="20.25" spans="1:1">
+      <c r="A258" s="5"/>
+    </row>
+    <row r="259" ht="20.25" spans="1:1">
+      <c r="A259" s="5"/>
+    </row>
+    <row r="260" ht="20.25" spans="1:1">
+      <c r="A260" s="5"/>
+    </row>
+    <row r="261" ht="20.25" spans="1:1">
+      <c r="A261" s="5"/>
+    </row>
+    <row r="262" ht="20.25" spans="1:1">
+      <c r="A262" s="5"/>
+    </row>
+    <row r="263" ht="20.25" spans="1:1">
+      <c r="A263" s="5"/>
+    </row>
+    <row r="264" ht="20.25" spans="1:1">
+      <c r="A264" s="5"/>
+    </row>
+    <row r="265" ht="20.25" spans="1:1">
+      <c r="A265" s="5"/>
+    </row>
+    <row r="266" ht="20.25" spans="1:1">
+      <c r="A266" s="5"/>
+    </row>
+    <row r="267" ht="20.25" spans="1:1">
+      <c r="A267" s="5"/>
+    </row>
+    <row r="268" ht="20.25" spans="1:1">
+      <c r="A268" s="5"/>
+    </row>
+    <row r="269" ht="20.25" spans="1:1">
+      <c r="A269" s="5"/>
+    </row>
+    <row r="270" ht="20.25" spans="1:1">
+      <c r="A270" s="5"/>
+    </row>
+    <row r="271" ht="20.25" spans="1:1">
+      <c r="A271" s="5"/>
+    </row>
+    <row r="272" ht="20.25" spans="1:1">
+      <c r="A272" s="5"/>
+    </row>
+    <row r="273" ht="20.25" spans="1:1">
+      <c r="A273" s="5"/>
+    </row>
+    <row r="274" ht="20.25" spans="1:1">
+      <c r="A274" s="5"/>
+    </row>
+    <row r="275" ht="20.25" spans="1:1">
+      <c r="A275" s="5"/>
+    </row>
+    <row r="276" ht="20.25" spans="1:1">
+      <c r="A276" s="5"/>
+    </row>
+    <row r="277" ht="20.25" spans="1:1">
+      <c r="A277" s="5"/>
+    </row>
+    <row r="278" ht="20.25" spans="1:1">
+      <c r="A278" s="5"/>
+    </row>
+    <row r="279" ht="20.25" spans="1:1">
+      <c r="A279" s="5"/>
+    </row>
+    <row r="280" ht="20.25" spans="1:1">
+      <c r="A280" s="5"/>
+    </row>
+    <row r="281" ht="20.25" spans="1:1">
+      <c r="A281" s="5"/>
+    </row>
+    <row r="282" ht="20.25" spans="1:1">
+      <c r="A282" s="5"/>
+    </row>
+    <row r="283" ht="20.25" spans="1:1">
+      <c r="A283" s="5"/>
+    </row>
+    <row r="284" ht="20.25" spans="1:1">
+      <c r="A284" s="5"/>
+    </row>
+    <row r="285" ht="20.25" spans="1:1">
+      <c r="A285" s="5"/>
+    </row>
+    <row r="286" ht="20.25" spans="1:1">
+      <c r="A286" s="5"/>
+    </row>
+    <row r="287" ht="20.25" spans="1:1">
+      <c r="A287" s="5"/>
+    </row>
+    <row r="288" ht="20.25" spans="1:1">
+      <c r="A288" s="5"/>
+    </row>
+    <row r="289" ht="20.25" spans="1:1">
+      <c r="A289" s="5"/>
+    </row>
+    <row r="290" ht="20.25" spans="1:1">
+      <c r="A290" s="5"/>
+    </row>
+    <row r="291" ht="20.25" spans="1:1">
+      <c r="A291" s="5"/>
+    </row>
+    <row r="292" ht="20.25" spans="1:1">
+      <c r="A292" s="5"/>
+    </row>
+    <row r="293" ht="20.25" spans="1:1">
+      <c r="A293" s="5"/>
+    </row>
+    <row r="294" ht="20.25" spans="1:1">
+      <c r="A294" s="5"/>
+    </row>
+    <row r="295" ht="20.25" spans="1:1">
+      <c r="A295" s="5"/>
+    </row>
+    <row r="296" ht="20.25" spans="1:1">
+      <c r="A296" s="5"/>
+    </row>
+    <row r="297" ht="20.25" spans="1:1">
+      <c r="A297" s="5"/>
+    </row>
+    <row r="298" ht="20.25" spans="1:1">
+      <c r="A298" s="5"/>
+    </row>
+    <row r="299" ht="20.25" spans="1:1">
+      <c r="A299" s="5"/>
+    </row>
+    <row r="300" ht="20.25" spans="1:1">
+      <c r="A300" s="5"/>
+    </row>
+    <row r="301" ht="20.25" spans="1:1">
+      <c r="A301" s="5"/>
+    </row>
+    <row r="302" ht="20.25" spans="1:1">
+      <c r="A302" s="5"/>
+    </row>
+    <row r="303" ht="20.25" spans="1:1">
+      <c r="A303" s="5"/>
+    </row>
+    <row r="304" ht="20.25" spans="1:1">
+      <c r="A304" s="5"/>
+    </row>
+    <row r="305" ht="20.25" spans="1:1">
+      <c r="A305" s="5"/>
+    </row>
+    <row r="306" ht="20.25" spans="1:1">
+      <c r="A306" s="5"/>
+    </row>
+    <row r="307" ht="20.25" spans="1:1">
+      <c r="A307" s="5"/>
+    </row>
+    <row r="308" ht="20.25" spans="1:1">
+      <c r="A308" s="5"/>
+    </row>
+    <row r="309" ht="20.25" spans="1:1">
+      <c r="A309" s="5"/>
+    </row>
+    <row r="310" ht="20.25" spans="1:1">
+      <c r="A310" s="5"/>
+    </row>
+    <row r="311" ht="20.25" spans="1:1">
+      <c r="A311" s="5"/>
+    </row>
+    <row r="312" ht="20.25" spans="1:1">
+      <c r="A312" s="5"/>
+    </row>
+    <row r="313" ht="20.25" spans="1:1">
+      <c r="A313" s="5"/>
+    </row>
+    <row r="314" ht="20.25" spans="1:1">
+      <c r="A314" s="5"/>
+    </row>
+    <row r="315" ht="20.25" spans="1:1">
+      <c r="A315" s="5"/>
+    </row>
+    <row r="316" ht="20.25" spans="1:1">
+      <c r="A316" s="5"/>
+    </row>
+    <row r="317" ht="20.25" spans="1:1">
+      <c r="A317" s="5"/>
+    </row>
+    <row r="318" ht="20.25" spans="1:1">
+      <c r="A318" s="5"/>
+    </row>
+    <row r="319" ht="20.25" spans="1:1">
+      <c r="A319" s="5"/>
+    </row>
+    <row r="320" ht="20.25" spans="1:1">
+      <c r="A320" s="5"/>
+    </row>
+    <row r="321" ht="20.25" spans="1:1">
+      <c r="A321" s="5"/>
+    </row>
+    <row r="322" ht="20.25" spans="1:1">
+      <c r="A322" s="5"/>
+    </row>
+    <row r="323" ht="20.25" spans="1:1">
+      <c r="A323" s="5"/>
+    </row>
+    <row r="324" ht="20.25" spans="1:1">
+      <c r="A324" s="5"/>
+    </row>
+    <row r="325" ht="20.25" spans="1:1">
+      <c r="A325" s="5"/>
+    </row>
+    <row r="326" ht="20.25" spans="1:1">
+      <c r="A326" s="5"/>
+    </row>
+    <row r="327" ht="20.25" spans="1:1">
+      <c r="A327" s="5"/>
+    </row>
+    <row r="328" ht="20.25" spans="1:1">
+      <c r="A328" s="5"/>
+    </row>
+    <row r="329" ht="20.25" spans="1:1">
+      <c r="A329" s="5"/>
+    </row>
+    <row r="330" ht="20.25" spans="1:1">
+      <c r="A330" s="5"/>
+    </row>
+    <row r="331" ht="20.25" spans="1:1">
+      <c r="A331" s="5"/>
+    </row>
+    <row r="332" ht="20.25" spans="1:1">
+      <c r="A332" s="5"/>
+    </row>
+    <row r="333" ht="20.25" spans="1:1">
+      <c r="A333" s="5"/>
+    </row>
+    <row r="334" ht="20.25" spans="1:1">
+      <c r="A334" s="5"/>
+    </row>
+    <row r="335" ht="20.25" spans="1:1">
+      <c r="A335" s="5"/>
+    </row>
+    <row r="336" ht="20.25" spans="1:1">
+      <c r="A336" s="5"/>
+    </row>
+    <row r="337" ht="20.25" spans="1:1">
+      <c r="A337" s="5"/>
+    </row>
+    <row r="338" ht="20.25" spans="1:1">
+      <c r="A338" s="5"/>
+    </row>
+    <row r="339" ht="20.25" spans="1:1">
+      <c r="A339" s="5"/>
+    </row>
+    <row r="340" ht="20.25" spans="1:1">
+      <c r="A340" s="5"/>
+    </row>
+    <row r="341" ht="20.25" spans="1:1">
+      <c r="A341" s="5"/>
+    </row>
+    <row r="342" ht="20.25" spans="1:1">
+      <c r="A342" s="5"/>
+    </row>
+    <row r="343" ht="20.25" spans="1:1">
+      <c r="A343" s="5"/>
+    </row>
+    <row r="344" ht="20.25" spans="1:1">
+      <c r="A344" s="5"/>
+    </row>
+    <row r="345" ht="20.25" spans="1:1">
+      <c r="A345" s="5"/>
+    </row>
+    <row r="346" ht="20.25" spans="1:1">
+      <c r="A346" s="5"/>
+    </row>
+    <row r="347" ht="20.25" spans="1:1">
+      <c r="A347" s="5"/>
+    </row>
+    <row r="348" ht="20.25" spans="1:1">
+      <c r="A348" s="5"/>
+    </row>
+    <row r="349" ht="20.25" spans="1:1">
+      <c r="A349" s="5"/>
+    </row>
+    <row r="350" ht="20.25" spans="1:1">
+      <c r="A350" s="5"/>
+    </row>
+    <row r="351" ht="20.25" spans="1:1">
+      <c r="A351" s="5"/>
+    </row>
+    <row r="352" ht="20.25" spans="1:1">
+      <c r="A352" s="5"/>
+    </row>
+    <row r="353" ht="20.25" spans="1:1">
+      <c r="A353" s="5"/>
+    </row>
+    <row r="354" ht="20.25" spans="1:1">
+      <c r="A354" s="5"/>
+    </row>
+    <row r="355" ht="20.25" spans="1:1">
+      <c r="A355" s="5"/>
+    </row>
+    <row r="356" ht="20.25" spans="1:1">
+      <c r="A356" s="5"/>
+    </row>
+    <row r="357" ht="20.25" spans="1:1">
+      <c r="A357" s="5"/>
+    </row>
+    <row r="358" ht="20.25" spans="1:1">
+      <c r="A358" s="5"/>
+    </row>
+    <row r="359" ht="20.25" spans="1:1">
+      <c r="A359" s="5"/>
+    </row>
+    <row r="360" ht="20.25" spans="1:1">
+      <c r="A360" s="5"/>
+    </row>
+    <row r="361" ht="20.25" spans="1:1">
+      <c r="A361" s="5"/>
+    </row>
+    <row r="362" ht="20.25" spans="1:1">
+      <c r="A362" s="5"/>
+    </row>
+    <row r="363" ht="20.25" spans="1:1">
+      <c r="A363" s="5"/>
+    </row>
+    <row r="364" ht="20.25" spans="1:1">
+      <c r="A364" s="5"/>
+    </row>
+    <row r="365" ht="20.25" spans="1:1">
+      <c r="A365" s="5"/>
+    </row>
+    <row r="366" ht="20.25" spans="1:1">
+      <c r="A366" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7424,15 +6985,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M366"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23008849557522" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="5" max="5" width="8.38461538461539"/>
-    <col min="6" max="6" width="15.6923076923077"/>
-    <col min="13" max="13" width="27.6153846153846" customWidth="1"/>
+    <col min="5" max="5" width="8.38053097345133"/>
+    <col min="6" max="6" width="15.6902654867257"/>
+    <col min="13" max="13" width="27.6194690265487" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.6" spans="1:13">
+    <row r="1" ht="20.25" spans="1:13">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -7444,7 +7005,7 @@
       </c>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" ht="19.6" spans="1:13">
+    <row r="2" ht="20.25" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -7463,7 +7024,7 @@
       </c>
       <c r="M2" s="5"/>
     </row>
-    <row r="3" ht="19.6" spans="1:13">
+    <row r="3" ht="20.25" spans="1:13">
       <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
@@ -7482,7 +7043,7 @@
       </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" ht="19.6" spans="1:13">
+    <row r="4" ht="20.25" spans="1:13">
       <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
@@ -7501,7 +7062,7 @@
       </c>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" ht="19.6" spans="1:13">
+    <row r="5" ht="20.25" spans="1:13">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -7520,7 +7081,7 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" ht="19.6" spans="1:13">
+    <row r="6" ht="20.25" spans="1:13">
       <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
@@ -7539,7 +7100,7 @@
       </c>
       <c r="M6" s="5"/>
     </row>
-    <row r="7" ht="19.6" spans="1:13">
+    <row r="7" ht="20.25" spans="1:13">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -7558,7 +7119,7 @@
       </c>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" ht="19.6" spans="1:13">
+    <row r="8" ht="20.25" spans="1:13">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
@@ -7577,7 +7138,7 @@
       </c>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" ht="19.6" spans="1:13">
+    <row r="9" ht="20.25" spans="1:13">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -7596,7 +7157,7 @@
       </c>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" ht="19.6" spans="1:13">
+    <row r="10" ht="20.25" spans="1:13">
       <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
@@ -7615,7 +7176,7 @@
       </c>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" ht="19.6" spans="1:13">
+    <row r="11" ht="20.25" spans="1:13">
       <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
@@ -7634,7 +7195,7 @@
       </c>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" ht="19.6" spans="1:13">
+    <row r="12" ht="20.25" spans="1:13">
       <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
@@ -7653,7 +7214,7 @@
       </c>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" ht="19.6" spans="1:13">
+    <row r="13" ht="20.25" spans="1:13">
       <c r="A13" s="5" t="s">
         <v>27</v>
       </c>
@@ -7672,7 +7233,7 @@
       </c>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" ht="19.6" spans="1:13">
+    <row r="14" ht="20.25" spans="1:13">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -7691,7 +7252,7 @@
       </c>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" ht="19.6" spans="1:13">
+    <row r="15" ht="20.25" spans="1:13">
       <c r="A15" s="5" t="s">
         <v>29</v>
       </c>
@@ -7710,7 +7271,7 @@
       </c>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" ht="19.6" spans="1:13">
+    <row r="16" ht="20.25" spans="1:13">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -7723,7 +7284,7 @@
       </c>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" ht="19.6" spans="1:13">
+    <row r="17" ht="20.25" spans="1:13">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -7736,7 +7297,7 @@
       </c>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" ht="19.6" spans="1:13">
+    <row r="18" ht="20.25" spans="1:13">
       <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
@@ -7749,7 +7310,7 @@
       </c>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" ht="19.6" spans="1:13">
+    <row r="19" ht="20.25" spans="1:13">
       <c r="A19" s="5" t="s">
         <v>34</v>
       </c>
@@ -7762,7 +7323,7 @@
       </c>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" ht="19.6" spans="1:13">
+    <row r="20" ht="20.25" spans="1:13">
       <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
@@ -7775,7 +7336,7 @@
       </c>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" ht="19.6" spans="1:13">
+    <row r="21" ht="20.25" spans="1:13">
       <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
@@ -7788,7 +7349,7 @@
       </c>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" ht="19.6" spans="1:13">
+    <row r="22" ht="20.25" spans="1:13">
       <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
@@ -7801,7 +7362,7 @@
       </c>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" ht="19.6" spans="1:13">
+    <row r="23" ht="20.25" spans="1:13">
       <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
@@ -7814,7 +7375,7 @@
       </c>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" ht="19.6" spans="1:13">
+    <row r="24" ht="20.25" spans="1:13">
       <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
@@ -7827,7 +7388,7 @@
       </c>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" ht="19.6" spans="1:13">
+    <row r="25" ht="20.25" spans="1:13">
       <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
@@ -7840,7 +7401,7 @@
       </c>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" ht="19.6" spans="1:13">
+    <row r="26" ht="20.25" spans="1:13">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
@@ -7853,7 +7414,7 @@
       </c>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" ht="19.6" spans="1:13">
+    <row r="27" ht="20.25" spans="1:13">
       <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
@@ -7866,7 +7427,7 @@
       </c>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" ht="19.6" spans="1:13">
+    <row r="28" ht="20.25" spans="1:13">
       <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
@@ -7879,7 +7440,7 @@
       </c>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" ht="19.6" spans="1:13">
+    <row r="29" ht="20.25" spans="1:13">
       <c r="A29" s="5" t="s">
         <v>44</v>
       </c>
@@ -7892,7 +7453,7 @@
       </c>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" ht="19.6" spans="1:13">
+    <row r="30" ht="20.25" spans="1:13">
       <c r="A30" s="5" t="s">
         <v>45</v>
       </c>
@@ -7905,7 +7466,7 @@
       </c>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" ht="19.6" spans="1:13">
+    <row r="31" ht="20.25" spans="1:13">
       <c r="A31" s="5" t="s">
         <v>46</v>
       </c>
@@ -7918,7 +7479,7 @@
       </c>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" ht="19.6" spans="1:13">
+    <row r="32" ht="20.25" spans="1:13">
       <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
@@ -7931,7 +7492,7 @@
       </c>
       <c r="M32" s="5"/>
     </row>
-    <row r="33" ht="19.6" spans="1:13">
+    <row r="33" ht="20.25" spans="1:13">
       <c r="A33" s="5" t="s">
         <v>48</v>
       </c>
@@ -7944,7 +7505,7 @@
       </c>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" ht="19.6" spans="1:13">
+    <row r="34" ht="20.25" spans="1:13">
       <c r="A34" s="5" t="s">
         <v>49</v>
       </c>
@@ -7957,7 +7518,7 @@
       </c>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" ht="19.6" spans="1:13">
+    <row r="35" ht="20.25" spans="1:13">
       <c r="A35" s="5" t="s">
         <v>50</v>
       </c>
@@ -7970,7 +7531,7 @@
       </c>
       <c r="M35" s="5"/>
     </row>
-    <row r="36" ht="19.6" spans="1:13">
+    <row r="36" ht="20.25" spans="1:13">
       <c r="A36" s="5" t="s">
         <v>51</v>
       </c>
@@ -7983,7 +7544,7 @@
       </c>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" ht="19.6" spans="1:13">
+    <row r="37" ht="20.25" spans="1:13">
       <c r="A37" s="5" t="s">
         <v>52</v>
       </c>
@@ -7996,7 +7557,7 @@
       </c>
       <c r="M37" s="5"/>
     </row>
-    <row r="38" ht="19.6" spans="1:13">
+    <row r="38" ht="20.25" spans="1:13">
       <c r="A38" s="5" t="s">
         <v>53</v>
       </c>
@@ -8009,7 +7570,7 @@
       </c>
       <c r="M38" s="5"/>
     </row>
-    <row r="39" ht="19.6" spans="1:13">
+    <row r="39" ht="20.25" spans="1:13">
       <c r="A39" s="5" t="s">
         <v>54</v>
       </c>
@@ -8022,7 +7583,7 @@
       </c>
       <c r="M39" s="5"/>
     </row>
-    <row r="40" ht="19.6" spans="1:13">
+    <row r="40" ht="20.25" spans="1:13">
       <c r="A40" s="5" t="s">
         <v>55</v>
       </c>
@@ -8035,7 +7596,7 @@
       </c>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" ht="19.6" spans="1:13">
+    <row r="41" ht="20.25" spans="1:13">
       <c r="A41" s="5" t="s">
         <v>56</v>
       </c>
@@ -8048,7 +7609,7 @@
       </c>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" ht="19.6" spans="1:13">
+    <row r="42" ht="20.25" spans="1:13">
       <c r="A42" s="5" t="s">
         <v>57</v>
       </c>
@@ -8061,7 +7622,7 @@
       </c>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" ht="19.6" spans="1:13">
+    <row r="43" ht="20.25" spans="1:13">
       <c r="A43" s="5" t="s">
         <v>58</v>
       </c>
@@ -8074,7 +7635,7 @@
       </c>
       <c r="M43" s="5"/>
     </row>
-    <row r="44" ht="19.6" spans="1:13">
+    <row r="44" ht="20.25" spans="1:13">
       <c r="A44" s="5" t="s">
         <v>59</v>
       </c>
@@ -8087,7 +7648,7 @@
       </c>
       <c r="M44" s="5"/>
     </row>
-    <row r="45" ht="19.6" spans="1:13">
+    <row r="45" ht="20.25" spans="1:13">
       <c r="A45" s="5" t="s">
         <v>60</v>
       </c>
@@ -8100,7 +7661,7 @@
       </c>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" ht="19.6" spans="1:13">
+    <row r="46" ht="20.25" spans="1:13">
       <c r="A46" s="5" t="s">
         <v>61</v>
       </c>
@@ -8113,7 +7674,7 @@
       </c>
       <c r="M46" s="5"/>
     </row>
-    <row r="47" ht="19.6" spans="1:13">
+    <row r="47" ht="20.25" spans="1:13">
       <c r="A47" s="5" t="s">
         <v>62</v>
       </c>
@@ -8126,7 +7687,7 @@
       </c>
       <c r="M47" s="5"/>
     </row>
-    <row r="48" ht="19.6" spans="1:13">
+    <row r="48" ht="20.25" spans="1:13">
       <c r="A48" s="5" t="s">
         <v>63</v>
       </c>
@@ -8139,7 +7700,7 @@
       </c>
       <c r="M48" s="5"/>
     </row>
-    <row r="49" ht="19.6" spans="1:13">
+    <row r="49" ht="20.25" spans="1:13">
       <c r="A49" s="5" t="s">
         <v>64</v>
       </c>
@@ -8152,7 +7713,7 @@
       </c>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" ht="19.6" spans="1:13">
+    <row r="50" ht="20.25" spans="1:13">
       <c r="A50" s="5" t="s">
         <v>65</v>
       </c>
@@ -8165,7 +7726,7 @@
       </c>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" ht="19.6" spans="1:13">
+    <row r="51" ht="20.25" spans="1:13">
       <c r="A51" s="5" t="s">
         <v>66</v>
       </c>
@@ -8178,7 +7739,7 @@
       </c>
       <c r="M51" s="5"/>
     </row>
-    <row r="52" ht="19.6" spans="1:13">
+    <row r="52" ht="20.25" spans="1:13">
       <c r="A52" s="5" t="s">
         <v>67</v>
       </c>
@@ -8191,7 +7752,7 @@
       </c>
       <c r="M52" s="5"/>
     </row>
-    <row r="53" ht="19.6" spans="1:13">
+    <row r="53" ht="20.25" spans="1:13">
       <c r="A53" s="5" t="s">
         <v>68</v>
       </c>
@@ -8204,7 +7765,7 @@
       </c>
       <c r="M53" s="5"/>
     </row>
-    <row r="54" ht="19.6" spans="1:13">
+    <row r="54" ht="20.25" spans="1:13">
       <c r="A54" s="5" t="s">
         <v>69</v>
       </c>
@@ -8217,7 +7778,7 @@
       </c>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" ht="19.6" spans="1:13">
+    <row r="55" ht="20.25" spans="1:13">
       <c r="A55" s="5" t="s">
         <v>70</v>
       </c>
@@ -8230,7 +7791,7 @@
       </c>
       <c r="M55" s="5"/>
     </row>
-    <row r="56" ht="19.6" spans="1:13">
+    <row r="56" ht="20.25" spans="1:13">
       <c r="A56" s="5" t="s">
         <v>71</v>
       </c>
@@ -8243,7 +7804,7 @@
       </c>
       <c r="M56" s="5"/>
     </row>
-    <row r="57" ht="19.6" spans="1:13">
+    <row r="57" ht="20.25" spans="1:13">
       <c r="A57" s="5" t="s">
         <v>72</v>
       </c>
@@ -8256,7 +7817,7 @@
       </c>
       <c r="M57" s="5"/>
     </row>
-    <row r="58" ht="19.6" spans="1:13">
+    <row r="58" ht="20.25" spans="1:13">
       <c r="A58" s="5" t="s">
         <v>73</v>
       </c>
@@ -8269,7 +7830,7 @@
       </c>
       <c r="M58" s="5"/>
     </row>
-    <row r="59" ht="19.6" spans="1:13">
+    <row r="59" ht="20.25" spans="1:13">
       <c r="A59" s="5" t="s">
         <v>74</v>
       </c>
@@ -8282,7 +7843,7 @@
       </c>
       <c r="M59" s="5"/>
     </row>
-    <row r="60" ht="19.6" spans="1:13">
+    <row r="60" ht="20.25" spans="1:13">
       <c r="A60" s="5" t="s">
         <v>75</v>
       </c>
@@ -8295,7 +7856,7 @@
       </c>
       <c r="M60" s="5"/>
     </row>
-    <row r="61" ht="19.6" spans="1:13">
+    <row r="61" ht="20.25" spans="1:13">
       <c r="A61" s="5" t="s">
         <v>76</v>
       </c>
@@ -8308,7 +7869,7 @@
       </c>
       <c r="M61" s="5"/>
     </row>
-    <row r="62" ht="19.6" spans="1:13">
+    <row r="62" ht="20.25" spans="1:13">
       <c r="A62" s="5" t="s">
         <v>77</v>
       </c>
@@ -8321,7 +7882,7 @@
       </c>
       <c r="M62" s="5"/>
     </row>
-    <row r="63" ht="19.6" spans="1:13">
+    <row r="63" ht="20.25" spans="1:13">
       <c r="A63" s="5" t="s">
         <v>78</v>
       </c>
@@ -8334,7 +7895,7 @@
       </c>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" ht="19.6" spans="1:13">
+    <row r="64" ht="20.25" spans="1:13">
       <c r="A64" s="5" t="s">
         <v>79</v>
       </c>
@@ -8347,7 +7908,7 @@
       </c>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" ht="19.6" spans="1:13">
+    <row r="65" ht="20.25" spans="1:13">
       <c r="A65" s="5" t="s">
         <v>80</v>
       </c>
@@ -8360,7 +7921,7 @@
       </c>
       <c r="M65" s="5"/>
     </row>
-    <row r="66" ht="19.6" spans="1:13">
+    <row r="66" ht="20.25" spans="1:13">
       <c r="A66" s="5" t="s">
         <v>81</v>
       </c>
@@ -8373,7 +7934,7 @@
       </c>
       <c r="M66" s="5"/>
     </row>
-    <row r="67" ht="19.6" spans="1:13">
+    <row r="67" ht="20.25" spans="1:13">
       <c r="A67" s="5" t="s">
         <v>82</v>
       </c>
@@ -8386,7 +7947,7 @@
       </c>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" ht="19.6" spans="1:13">
+    <row r="68" ht="20.25" spans="1:13">
       <c r="A68" s="5" t="s">
         <v>83</v>
       </c>
@@ -8399,7 +7960,7 @@
       </c>
       <c r="M68" s="5"/>
     </row>
-    <row r="69" ht="19.6" spans="1:13">
+    <row r="69" ht="20.25" spans="1:13">
       <c r="A69" s="5" t="s">
         <v>84</v>
       </c>
@@ -8412,7 +7973,7 @@
       </c>
       <c r="M69" s="5"/>
     </row>
-    <row r="70" ht="19.6" spans="1:13">
+    <row r="70" ht="20.25" spans="1:13">
       <c r="A70" s="5" t="s">
         <v>85</v>
       </c>
@@ -8425,7 +7986,7 @@
       </c>
       <c r="M70" s="5"/>
     </row>
-    <row r="71" ht="19.6" spans="1:13">
+    <row r="71" ht="20.25" spans="1:13">
       <c r="A71" s="5" t="s">
         <v>86</v>
       </c>
@@ -8438,7 +7999,7 @@
       </c>
       <c r="M71" s="5"/>
     </row>
-    <row r="72" ht="19.6" spans="1:13">
+    <row r="72" ht="20.25" spans="1:13">
       <c r="A72" s="5" t="s">
         <v>87</v>
       </c>
@@ -8451,7 +8012,7 @@
       </c>
       <c r="M72" s="5"/>
     </row>
-    <row r="73" ht="19.6" spans="1:13">
+    <row r="73" ht="20.25" spans="1:13">
       <c r="A73" s="5" t="s">
         <v>88</v>
       </c>
@@ -8464,7 +8025,7 @@
       </c>
       <c r="M73" s="5"/>
     </row>
-    <row r="74" ht="19.6" spans="1:13">
+    <row r="74" ht="20.25" spans="1:13">
       <c r="A74" s="5" t="s">
         <v>89</v>
       </c>
@@ -8477,7 +8038,7 @@
       </c>
       <c r="M74" s="5"/>
     </row>
-    <row r="75" ht="19.6" spans="1:13">
+    <row r="75" ht="20.25" spans="1:13">
       <c r="A75" s="5" t="s">
         <v>90</v>
       </c>
@@ -8490,7 +8051,7 @@
       </c>
       <c r="M75" s="5"/>
     </row>
-    <row r="76" ht="19.6" spans="1:13">
+    <row r="76" ht="20.25" spans="1:13">
       <c r="A76" s="5" t="s">
         <v>91</v>
       </c>
@@ -8503,7 +8064,7 @@
       </c>
       <c r="M76" s="5"/>
     </row>
-    <row r="77" ht="19.6" spans="1:13">
+    <row r="77" ht="20.25" spans="1:13">
       <c r="A77" s="5" t="s">
         <v>92</v>
       </c>
@@ -8516,7 +8077,7 @@
       </c>
       <c r="M77" s="5"/>
     </row>
-    <row r="78" ht="19.6" spans="1:13">
+    <row r="78" ht="20.25" spans="1:13">
       <c r="A78" s="5" t="s">
         <v>93</v>
       </c>
@@ -8529,7 +8090,7 @@
       </c>
       <c r="M78" s="5"/>
     </row>
-    <row r="79" ht="19.6" spans="1:13">
+    <row r="79" ht="20.25" spans="1:13">
       <c r="A79" s="5" t="s">
         <v>94</v>
       </c>
@@ -8542,7 +8103,7 @@
       </c>
       <c r="M79" s="5"/>
     </row>
-    <row r="80" ht="19.6" spans="1:13">
+    <row r="80" ht="20.25" spans="1:13">
       <c r="A80" s="5" t="s">
         <v>95</v>
       </c>
@@ -8555,7 +8116,7 @@
       </c>
       <c r="M80" s="5"/>
     </row>
-    <row r="81" ht="19.6" spans="1:13">
+    <row r="81" ht="20.25" spans="1:13">
       <c r="A81" s="5" t="s">
         <v>96</v>
       </c>
@@ -8568,7 +8129,7 @@
       </c>
       <c r="M81" s="5"/>
     </row>
-    <row r="82" ht="19.6" spans="1:13">
+    <row r="82" ht="20.25" spans="1:13">
       <c r="A82" s="5" t="s">
         <v>97</v>
       </c>
@@ -8581,7 +8142,7 @@
       </c>
       <c r="M82" s="5"/>
     </row>
-    <row r="83" ht="19.6" spans="1:13">
+    <row r="83" ht="20.25" spans="1:13">
       <c r="A83" s="5" t="s">
         <v>98</v>
       </c>
@@ -8594,7 +8155,7 @@
       </c>
       <c r="M83" s="5"/>
     </row>
-    <row r="84" ht="19.6" spans="1:13">
+    <row r="84" ht="20.25" spans="1:13">
       <c r="A84" s="5" t="s">
         <v>99</v>
       </c>
@@ -8607,7 +8168,7 @@
       </c>
       <c r="M84" s="5"/>
     </row>
-    <row r="85" ht="19.6" spans="1:13">
+    <row r="85" ht="20.25" spans="1:13">
       <c r="A85" s="5" t="s">
         <v>100</v>
       </c>
@@ -8620,7 +8181,7 @@
       </c>
       <c r="M85" s="5"/>
     </row>
-    <row r="86" ht="19.6" spans="1:13">
+    <row r="86" ht="20.25" spans="1:13">
       <c r="A86" s="5" t="s">
         <v>101</v>
       </c>
@@ -8633,7 +8194,7 @@
       </c>
       <c r="M86" s="5"/>
     </row>
-    <row r="87" ht="19.6" spans="1:13">
+    <row r="87" ht="20.25" spans="1:13">
       <c r="A87" s="5" t="s">
         <v>102</v>
       </c>
@@ -8646,7 +8207,7 @@
       </c>
       <c r="M87" s="5"/>
     </row>
-    <row r="88" ht="19.6" spans="1:13">
+    <row r="88" ht="20.25" spans="1:13">
       <c r="A88" s="5" t="s">
         <v>103</v>
       </c>
@@ -8659,7 +8220,7 @@
       </c>
       <c r="M88" s="5"/>
     </row>
-    <row r="89" ht="19.6" spans="1:13">
+    <row r="89" ht="20.25" spans="1:13">
       <c r="A89" s="5" t="s">
         <v>104</v>
       </c>
@@ -8672,7 +8233,7 @@
       </c>
       <c r="M89" s="5"/>
     </row>
-    <row r="90" ht="19.6" spans="1:13">
+    <row r="90" ht="20.25" spans="1:13">
       <c r="A90" s="5" t="s">
         <v>105</v>
       </c>
@@ -8685,7 +8246,7 @@
       </c>
       <c r="M90" s="5"/>
     </row>
-    <row r="91" ht="19.6" spans="1:13">
+    <row r="91" ht="20.25" spans="1:13">
       <c r="A91" s="5" t="s">
         <v>106</v>
       </c>
@@ -8698,7 +8259,7 @@
       </c>
       <c r="M91" s="5"/>
     </row>
-    <row r="92" ht="19.6" spans="1:13">
+    <row r="92" ht="20.25" spans="1:13">
       <c r="A92" s="5" t="s">
         <v>107</v>
       </c>
@@ -8711,7 +8272,7 @@
       </c>
       <c r="M92" s="5"/>
     </row>
-    <row r="93" ht="19.6" spans="1:13">
+    <row r="93" ht="20.25" spans="1:13">
       <c r="A93" s="5" t="s">
         <v>108</v>
       </c>
@@ -8724,7 +8285,7 @@
       </c>
       <c r="M93" s="5"/>
     </row>
-    <row r="94" ht="19.6" spans="1:13">
+    <row r="94" ht="20.25" spans="1:13">
       <c r="A94" s="5" t="s">
         <v>109</v>
       </c>
@@ -8737,7 +8298,7 @@
       </c>
       <c r="M94" s="5"/>
     </row>
-    <row r="95" ht="19.6" spans="1:13">
+    <row r="95" ht="20.25" spans="1:13">
       <c r="A95" s="5" t="s">
         <v>110</v>
       </c>
@@ -8750,7 +8311,7 @@
       </c>
       <c r="M95" s="5"/>
     </row>
-    <row r="96" ht="19.6" spans="1:13">
+    <row r="96" ht="20.25" spans="1:13">
       <c r="A96" s="5" t="s">
         <v>111</v>
       </c>
@@ -8763,7 +8324,7 @@
       </c>
       <c r="M96" s="5"/>
     </row>
-    <row r="97" ht="19.6" spans="1:13">
+    <row r="97" ht="20.25" spans="1:13">
       <c r="A97" s="5" t="s">
         <v>112</v>
       </c>
@@ -8776,7 +8337,7 @@
       </c>
       <c r="M97" s="5"/>
     </row>
-    <row r="98" ht="19.6" spans="1:13">
+    <row r="98" ht="20.25" spans="1:13">
       <c r="A98" s="5" t="s">
         <v>113</v>
       </c>
@@ -8789,7 +8350,7 @@
       </c>
       <c r="M98" s="5"/>
     </row>
-    <row r="99" ht="19.6" spans="1:13">
+    <row r="99" ht="20.25" spans="1:13">
       <c r="A99" s="5" t="s">
         <v>114</v>
       </c>
@@ -8802,7 +8363,7 @@
       </c>
       <c r="M99" s="5"/>
     </row>
-    <row r="100" ht="19.6" spans="1:13">
+    <row r="100" ht="20.25" spans="1:13">
       <c r="A100" s="5" t="s">
         <v>115</v>
       </c>
@@ -8815,7 +8376,7 @@
       </c>
       <c r="M100" s="5"/>
     </row>
-    <row r="101" ht="19.6" spans="1:13">
+    <row r="101" ht="20.25" spans="1:13">
       <c r="A101" s="5" t="s">
         <v>116</v>
       </c>
@@ -8828,7 +8389,7 @@
       </c>
       <c r="M101" s="5"/>
     </row>
-    <row r="102" ht="19.6" spans="1:13">
+    <row r="102" ht="20.25" spans="1:13">
       <c r="A102" s="5" t="s">
         <v>117</v>
       </c>
@@ -8841,7 +8402,7 @@
       </c>
       <c r="M102" s="5"/>
     </row>
-    <row r="103" ht="19.6" spans="1:13">
+    <row r="103" ht="20.25" spans="1:13">
       <c r="A103" s="5" t="s">
         <v>118</v>
       </c>
@@ -8854,7 +8415,7 @@
       </c>
       <c r="M103" s="5"/>
     </row>
-    <row r="104" ht="19.6" spans="1:13">
+    <row r="104" ht="20.25" spans="1:13">
       <c r="A104" s="5" t="s">
         <v>119</v>
       </c>
@@ -8867,7 +8428,7 @@
       </c>
       <c r="M104" s="5"/>
     </row>
-    <row r="105" ht="19.6" spans="1:13">
+    <row r="105" ht="20.25" spans="1:13">
       <c r="A105" s="5" t="s">
         <v>120</v>
       </c>
@@ -8880,7 +8441,7 @@
       </c>
       <c r="M105" s="5"/>
     </row>
-    <row r="106" ht="19.6" spans="1:13">
+    <row r="106" ht="20.25" spans="1:13">
       <c r="A106" s="5" t="s">
         <v>121</v>
       </c>
@@ -8893,7 +8454,7 @@
       </c>
       <c r="M106" s="5"/>
     </row>
-    <row r="107" ht="19.6" spans="1:13">
+    <row r="107" ht="20.25" spans="1:13">
       <c r="A107" s="5" t="s">
         <v>122</v>
       </c>
@@ -8906,7 +8467,7 @@
       </c>
       <c r="M107" s="5"/>
     </row>
-    <row r="108" ht="19.6" spans="1:13">
+    <row r="108" ht="20.25" spans="1:13">
       <c r="A108" s="5" t="s">
         <v>123</v>
       </c>
@@ -8919,7 +8480,7 @@
       </c>
       <c r="M108" s="5"/>
     </row>
-    <row r="109" ht="19.6" spans="1:13">
+    <row r="109" ht="20.25" spans="1:13">
       <c r="A109" s="5" t="s">
         <v>124</v>
       </c>
@@ -8932,7 +8493,7 @@
       </c>
       <c r="M109" s="5"/>
     </row>
-    <row r="110" ht="19.6" spans="1:13">
+    <row r="110" ht="20.25" spans="1:13">
       <c r="A110" s="5" t="s">
         <v>125</v>
       </c>
@@ -8945,7 +8506,7 @@
       </c>
       <c r="M110" s="5"/>
     </row>
-    <row r="111" ht="19.6" spans="1:13">
+    <row r="111" ht="20.25" spans="1:13">
       <c r="A111" s="5" t="s">
         <v>126</v>
       </c>
@@ -8958,7 +8519,7 @@
       </c>
       <c r="M111" s="5"/>
     </row>
-    <row r="112" ht="19.6" spans="1:13">
+    <row r="112" ht="20.25" spans="1:13">
       <c r="A112" s="5" t="s">
         <v>127</v>
       </c>
@@ -8971,7 +8532,7 @@
       </c>
       <c r="M112" s="5"/>
     </row>
-    <row r="113" ht="19.6" spans="1:13">
+    <row r="113" ht="20.25" spans="1:13">
       <c r="A113" s="5" t="s">
         <v>128</v>
       </c>
@@ -8984,7 +8545,7 @@
       </c>
       <c r="M113" s="5"/>
     </row>
-    <row r="114" ht="19.6" spans="1:13">
+    <row r="114" ht="20.25" spans="1:13">
       <c r="A114" s="5" t="s">
         <v>129</v>
       </c>
@@ -8997,7 +8558,7 @@
       </c>
       <c r="M114" s="5"/>
     </row>
-    <row r="115" ht="19.6" spans="1:13">
+    <row r="115" ht="20.25" spans="1:13">
       <c r="A115" s="5" t="s">
         <v>130</v>
       </c>
@@ -9010,7 +8571,7 @@
       </c>
       <c r="M115" s="5"/>
     </row>
-    <row r="116" ht="19.6" spans="1:13">
+    <row r="116" ht="20.25" spans="1:13">
       <c r="A116" s="5" t="s">
         <v>131</v>
       </c>
@@ -9023,7 +8584,7 @@
       </c>
       <c r="M116" s="5"/>
     </row>
-    <row r="117" ht="19.6" spans="1:13">
+    <row r="117" ht="20.25" spans="1:13">
       <c r="A117" s="5" t="s">
         <v>132</v>
       </c>
@@ -9036,7 +8597,7 @@
       </c>
       <c r="M117" s="5"/>
     </row>
-    <row r="118" ht="19.6" spans="1:13">
+    <row r="118" ht="20.25" spans="1:13">
       <c r="A118" s="5" t="s">
         <v>133</v>
       </c>
@@ -9049,7 +8610,7 @@
       </c>
       <c r="M118" s="5"/>
     </row>
-    <row r="119" ht="19.6" spans="1:13">
+    <row r="119" ht="20.25" spans="1:13">
       <c r="A119" s="5" t="s">
         <v>134</v>
       </c>
@@ -9062,7 +8623,7 @@
       </c>
       <c r="M119" s="5"/>
     </row>
-    <row r="120" ht="19.6" spans="1:13">
+    <row r="120" ht="20.25" spans="1:13">
       <c r="A120" s="5" t="s">
         <v>135</v>
       </c>
@@ -9075,7 +8636,7 @@
       </c>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" ht="19.6" spans="1:13">
+    <row r="121" ht="20.25" spans="1:13">
       <c r="A121" s="5" t="s">
         <v>136</v>
       </c>
@@ -9088,7 +8649,7 @@
       </c>
       <c r="M121" s="5"/>
     </row>
-    <row r="122" ht="19.6" spans="1:13">
+    <row r="122" ht="20.25" spans="1:13">
       <c r="A122" s="5" t="s">
         <v>137</v>
       </c>
@@ -9101,7 +8662,7 @@
       </c>
       <c r="M122" s="5"/>
     </row>
-    <row r="123" ht="19.6" spans="1:13">
+    <row r="123" ht="20.25" spans="1:13">
       <c r="A123" s="5" t="s">
         <v>138</v>
       </c>
@@ -9114,7 +8675,7 @@
       </c>
       <c r="M123" s="5"/>
     </row>
-    <row r="124" ht="19.6" spans="1:13">
+    <row r="124" ht="20.25" spans="1:13">
       <c r="A124" s="5" t="s">
         <v>139</v>
       </c>
@@ -9127,7 +8688,7 @@
       </c>
       <c r="M124" s="5"/>
     </row>
-    <row r="125" ht="19.6" spans="1:13">
+    <row r="125" ht="20.25" spans="1:13">
       <c r="A125" s="5" t="s">
         <v>140</v>
       </c>
@@ -9140,7 +8701,7 @@
       </c>
       <c r="M125" s="5"/>
     </row>
-    <row r="126" ht="19.6" spans="1:13">
+    <row r="126" ht="20.25" spans="1:13">
       <c r="A126" s="5" t="s">
         <v>141</v>
       </c>
@@ -9153,7 +8714,7 @@
       </c>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" ht="19.6" spans="1:13">
+    <row r="127" ht="20.25" spans="1:13">
       <c r="A127" s="5" t="s">
         <v>142</v>
       </c>
@@ -9166,7 +8727,7 @@
       </c>
       <c r="M127" s="5"/>
     </row>
-    <row r="128" ht="19.6" spans="1:13">
+    <row r="128" ht="20.25" spans="1:13">
       <c r="A128" s="5" t="s">
         <v>143</v>
       </c>
@@ -9179,7 +8740,7 @@
       </c>
       <c r="M128" s="5"/>
     </row>
-    <row r="129" ht="19.6" spans="1:13">
+    <row r="129" ht="20.25" spans="1:13">
       <c r="A129" s="5" t="s">
         <v>144</v>
       </c>
@@ -9192,7 +8753,7 @@
       </c>
       <c r="M129" s="5"/>
     </row>
-    <row r="130" ht="19.6" spans="1:13">
+    <row r="130" ht="20.25" spans="1:13">
       <c r="A130" s="5" t="s">
         <v>145</v>
       </c>
@@ -9205,7 +8766,7 @@
       </c>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" ht="19.6" spans="1:13">
+    <row r="131" ht="20.25" spans="1:13">
       <c r="A131" s="5" t="s">
         <v>146</v>
       </c>
@@ -9218,7 +8779,7 @@
       </c>
       <c r="M131" s="5"/>
     </row>
-    <row r="132" ht="19.6" spans="1:13">
+    <row r="132" ht="20.25" spans="1:13">
       <c r="A132" s="5" t="s">
         <v>147</v>
       </c>
@@ -9231,7 +8792,7 @@
       </c>
       <c r="M132" s="5"/>
     </row>
-    <row r="133" ht="19.6" spans="1:13">
+    <row r="133" ht="20.25" spans="1:13">
       <c r="A133" s="5" t="s">
         <v>148</v>
       </c>
@@ -9244,7 +8805,7 @@
       </c>
       <c r="M133" s="5"/>
     </row>
-    <row r="134" ht="19.6" spans="1:13">
+    <row r="134" ht="20.25" spans="1:13">
       <c r="A134" s="5" t="s">
         <v>149</v>
       </c>
@@ -9257,7 +8818,7 @@
       </c>
       <c r="M134" s="5"/>
     </row>
-    <row r="135" ht="19.6" spans="1:13">
+    <row r="135" ht="20.25" spans="1:13">
       <c r="A135" s="5" t="s">
         <v>150</v>
       </c>
@@ -9270,7 +8831,7 @@
       </c>
       <c r="M135" s="5"/>
     </row>
-    <row r="136" ht="19.6" spans="1:13">
+    <row r="136" ht="20.25" spans="1:13">
       <c r="A136" s="5" t="s">
         <v>151</v>
       </c>
@@ -9283,7 +8844,7 @@
       </c>
       <c r="M136" s="5"/>
     </row>
-    <row r="137" ht="19.6" spans="1:13">
+    <row r="137" ht="20.25" spans="1:13">
       <c r="A137" s="5" t="s">
         <v>152</v>
       </c>
@@ -9296,7 +8857,7 @@
       </c>
       <c r="M137" s="5"/>
     </row>
-    <row r="138" ht="19.6" spans="1:13">
+    <row r="138" ht="20.25" spans="1:13">
       <c r="A138" s="5" t="s">
         <v>153</v>
       </c>
@@ -9309,7 +8870,7 @@
       </c>
       <c r="M138" s="5"/>
     </row>
-    <row r="139" ht="19.6" spans="1:13">
+    <row r="139" ht="20.25" spans="1:13">
       <c r="A139" s="5" t="s">
         <v>154</v>
       </c>
@@ -9322,7 +8883,7 @@
       </c>
       <c r="M139" s="5"/>
     </row>
-    <row r="140" ht="19.6" spans="1:13">
+    <row r="140" ht="20.25" spans="1:13">
       <c r="A140" s="5" t="s">
         <v>155</v>
       </c>
@@ -9335,7 +8896,7 @@
       </c>
       <c r="M140" s="5"/>
     </row>
-    <row r="141" ht="19.6" spans="1:13">
+    <row r="141" ht="20.25" spans="1:13">
       <c r="A141" s="5" t="s">
         <v>156</v>
       </c>
@@ -9348,7 +8909,7 @@
       </c>
       <c r="M141" s="5"/>
     </row>
-    <row r="142" ht="19.6" spans="1:13">
+    <row r="142" ht="20.25" spans="1:13">
       <c r="A142" s="5" t="s">
         <v>157</v>
       </c>
@@ -9361,7 +8922,7 @@
       </c>
       <c r="M142" s="5"/>
     </row>
-    <row r="143" ht="19.6" spans="1:13">
+    <row r="143" ht="20.25" spans="1:13">
       <c r="A143" s="5" t="s">
         <v>158</v>
       </c>
@@ -9374,7 +8935,7 @@
       </c>
       <c r="M143" s="5"/>
     </row>
-    <row r="144" ht="19.6" spans="1:13">
+    <row r="144" ht="20.25" spans="1:13">
       <c r="A144" s="5" t="s">
         <v>159</v>
       </c>
@@ -9387,7 +8948,7 @@
       </c>
       <c r="M144" s="5"/>
     </row>
-    <row r="145" ht="19.6" spans="1:13">
+    <row r="145" ht="20.25" spans="1:13">
       <c r="A145" s="5" t="s">
         <v>160</v>
       </c>
@@ -9400,7 +8961,7 @@
       </c>
       <c r="M145" s="5"/>
     </row>
-    <row r="146" ht="19.6" spans="1:13">
+    <row r="146" ht="20.25" spans="1:13">
       <c r="A146" s="5" t="s">
         <v>161</v>
       </c>
@@ -9413,7 +8974,7 @@
       </c>
       <c r="M146" s="5"/>
     </row>
-    <row r="147" ht="19.6" spans="1:13">
+    <row r="147" ht="20.25" spans="1:13">
       <c r="A147" s="5" t="s">
         <v>162</v>
       </c>
@@ -9426,7 +8987,7 @@
       </c>
       <c r="M147" s="5"/>
     </row>
-    <row r="148" ht="19.6" spans="1:13">
+    <row r="148" ht="20.25" spans="1:13">
       <c r="A148" s="5" t="s">
         <v>163</v>
       </c>
@@ -9439,7 +9000,7 @@
       </c>
       <c r="M148" s="5"/>
     </row>
-    <row r="149" ht="19.6" spans="1:13">
+    <row r="149" ht="20.25" spans="1:13">
       <c r="A149" s="5" t="s">
         <v>164</v>
       </c>
@@ -9452,7 +9013,7 @@
       </c>
       <c r="M149" s="5"/>
     </row>
-    <row r="150" ht="19.6" spans="1:13">
+    <row r="150" ht="20.25" spans="1:13">
       <c r="A150" s="5" t="s">
         <v>165</v>
       </c>
@@ -9465,7 +9026,7 @@
       </c>
       <c r="M150" s="5"/>
     </row>
-    <row r="151" ht="19.6" spans="1:13">
+    <row r="151" ht="20.25" spans="1:13">
       <c r="A151" s="5" t="s">
         <v>166</v>
       </c>
@@ -9478,7 +9039,7 @@
       </c>
       <c r="M151" s="5"/>
     </row>
-    <row r="152" ht="19.6" spans="1:13">
+    <row r="152" ht="20.25" spans="1:13">
       <c r="A152" s="5" t="s">
         <v>167</v>
       </c>
@@ -9491,7 +9052,7 @@
       </c>
       <c r="M152" s="5"/>
     </row>
-    <row r="153" ht="19.6" spans="1:13">
+    <row r="153" ht="20.25" spans="1:13">
       <c r="A153" s="5" t="s">
         <v>168</v>
       </c>
@@ -9504,7 +9065,7 @@
       </c>
       <c r="M153" s="5"/>
     </row>
-    <row r="154" ht="19.6" spans="1:13">
+    <row r="154" ht="20.25" spans="1:13">
       <c r="A154" s="5" t="s">
         <v>169</v>
       </c>
@@ -9517,7 +9078,7 @@
       </c>
       <c r="M154" s="5"/>
     </row>
-    <row r="155" ht="19.6" spans="1:13">
+    <row r="155" ht="20.25" spans="1:13">
       <c r="A155" s="5" t="s">
         <v>170</v>
       </c>
@@ -9530,7 +9091,7 @@
       </c>
       <c r="M155" s="5"/>
     </row>
-    <row r="156" ht="19.6" spans="1:13">
+    <row r="156" ht="20.25" spans="1:13">
       <c r="A156" s="5" t="s">
         <v>171</v>
       </c>
@@ -9543,7 +9104,7 @@
       </c>
       <c r="M156" s="5"/>
     </row>
-    <row r="157" ht="19.6" spans="1:13">
+    <row r="157" ht="20.25" spans="1:13">
       <c r="A157" s="5" t="s">
         <v>172</v>
       </c>
@@ -9556,7 +9117,7 @@
       </c>
       <c r="M157" s="5"/>
     </row>
-    <row r="158" ht="19.6" spans="1:13">
+    <row r="158" ht="20.25" spans="1:13">
       <c r="A158" s="5" t="s">
         <v>173</v>
       </c>
@@ -9569,7 +9130,7 @@
       </c>
       <c r="M158" s="5"/>
     </row>
-    <row r="159" ht="19.6" spans="1:13">
+    <row r="159" ht="20.25" spans="1:13">
       <c r="A159" s="5" t="s">
         <v>174</v>
       </c>
@@ -9582,7 +9143,7 @@
       </c>
       <c r="M159" s="5"/>
     </row>
-    <row r="160" ht="19.6" spans="1:13">
+    <row r="160" ht="20.25" spans="1:13">
       <c r="A160" s="5" t="s">
         <v>175</v>
       </c>
@@ -9595,7 +9156,7 @@
       </c>
       <c r="M160" s="5"/>
     </row>
-    <row r="161" ht="19.6" spans="1:13">
+    <row r="161" ht="20.25" spans="1:13">
       <c r="A161" s="5" t="s">
         <v>176</v>
       </c>
@@ -9608,7 +9169,7 @@
       </c>
       <c r="M161" s="5"/>
     </row>
-    <row r="162" ht="19.6" spans="1:13">
+    <row r="162" ht="20.25" spans="1:13">
       <c r="A162" s="5" t="s">
         <v>177</v>
       </c>
@@ -9621,7 +9182,7 @@
       </c>
       <c r="M162" s="5"/>
     </row>
-    <row r="163" ht="19.6" spans="1:13">
+    <row r="163" ht="20.25" spans="1:13">
       <c r="A163" s="5" t="s">
         <v>178</v>
       </c>
@@ -9634,7 +9195,7 @@
       </c>
       <c r="M163" s="5"/>
     </row>
-    <row r="164" ht="19.6" spans="1:13">
+    <row r="164" ht="20.25" spans="1:13">
       <c r="A164" s="5" t="s">
         <v>179</v>
       </c>
@@ -9647,7 +9208,7 @@
       </c>
       <c r="M164" s="5"/>
     </row>
-    <row r="165" ht="19.6" spans="1:13">
+    <row r="165" ht="20.25" spans="1:13">
       <c r="A165" s="5" t="s">
         <v>180</v>
       </c>
@@ -9660,7 +9221,7 @@
       </c>
       <c r="M165" s="5"/>
     </row>
-    <row r="166" ht="19.6" spans="1:13">
+    <row r="166" ht="20.25" spans="1:13">
       <c r="A166" s="5" t="s">
         <v>181</v>
       </c>
@@ -9673,7 +9234,7 @@
       </c>
       <c r="M166" s="5"/>
     </row>
-    <row r="167" ht="19.6" spans="1:13">
+    <row r="167" ht="20.25" spans="1:13">
       <c r="A167" s="5" t="s">
         <v>182</v>
       </c>
@@ -9686,7 +9247,7 @@
       </c>
       <c r="M167" s="5"/>
     </row>
-    <row r="168" ht="19.6" spans="1:13">
+    <row r="168" ht="20.25" spans="1:13">
       <c r="A168" s="5" t="s">
         <v>183</v>
       </c>
@@ -9699,7 +9260,7 @@
       </c>
       <c r="M168" s="5"/>
     </row>
-    <row r="169" ht="19.6" spans="1:13">
+    <row r="169" ht="20.25" spans="1:13">
       <c r="A169" s="5" t="s">
         <v>184</v>
       </c>
@@ -9712,7 +9273,7 @@
       </c>
       <c r="M169" s="5"/>
     </row>
-    <row r="170" ht="19.6" spans="1:13">
+    <row r="170" ht="20.25" spans="1:13">
       <c r="A170" s="5" t="s">
         <v>185</v>
       </c>
@@ -9725,7 +9286,7 @@
       </c>
       <c r="M170" s="5"/>
     </row>
-    <row r="171" ht="19.6" spans="1:13">
+    <row r="171" ht="20.25" spans="1:13">
       <c r="A171" s="5" t="s">
         <v>186</v>
       </c>
@@ -9738,7 +9299,7 @@
       </c>
       <c r="M171" s="5"/>
     </row>
-    <row r="172" ht="19.6" spans="1:13">
+    <row r="172" ht="20.25" spans="1:13">
       <c r="A172" s="5" t="s">
         <v>187</v>
       </c>
@@ -9751,7 +9312,7 @@
       </c>
       <c r="M172" s="5"/>
     </row>
-    <row r="173" ht="19.6" spans="1:13">
+    <row r="173" ht="20.25" spans="1:13">
       <c r="A173" s="5" t="s">
         <v>188</v>
       </c>
@@ -9764,7 +9325,7 @@
       </c>
       <c r="M173" s="5"/>
     </row>
-    <row r="174" ht="19.6" spans="1:13">
+    <row r="174" ht="20.25" spans="1:13">
       <c r="A174" s="5" t="s">
         <v>189</v>
       </c>
@@ -9777,7 +9338,7 @@
       </c>
       <c r="M174" s="5"/>
     </row>
-    <row r="175" ht="19.6" spans="1:13">
+    <row r="175" ht="20.25" spans="1:13">
       <c r="A175" s="5" t="s">
         <v>190</v>
       </c>
@@ -9790,7 +9351,7 @@
       </c>
       <c r="M175" s="5"/>
     </row>
-    <row r="176" ht="19.6" spans="1:13">
+    <row r="176" ht="20.25" spans="1:13">
       <c r="A176" s="5" t="s">
         <v>191</v>
       </c>
@@ -9803,7 +9364,7 @@
       </c>
       <c r="M176" s="5"/>
     </row>
-    <row r="177" ht="19.6" spans="1:13">
+    <row r="177" ht="20.25" spans="1:13">
       <c r="A177" s="5" t="s">
         <v>192</v>
       </c>
@@ -9816,7 +9377,7 @@
       </c>
       <c r="M177" s="5"/>
     </row>
-    <row r="178" ht="19.6" spans="1:13">
+    <row r="178" ht="20.25" spans="1:13">
       <c r="A178" s="5" t="s">
         <v>193</v>
       </c>
@@ -9829,7 +9390,7 @@
       </c>
       <c r="M178" s="5"/>
     </row>
-    <row r="179" ht="19.6" spans="1:13">
+    <row r="179" ht="20.25" spans="1:13">
       <c r="A179" s="5" t="s">
         <v>194</v>
       </c>
@@ -9842,7 +9403,7 @@
       </c>
       <c r="M179" s="5"/>
     </row>
-    <row r="180" ht="19.6" spans="1:13">
+    <row r="180" ht="20.25" spans="1:13">
       <c r="A180" s="5" t="s">
         <v>195</v>
       </c>
@@ -9855,7 +9416,7 @@
       </c>
       <c r="M180" s="5"/>
     </row>
-    <row r="181" ht="19.6" spans="1:13">
+    <row r="181" ht="20.25" spans="1:13">
       <c r="A181" s="5" t="s">
         <v>196</v>
       </c>
@@ -9868,7 +9429,7 @@
       </c>
       <c r="M181" s="5"/>
     </row>
-    <row r="182" ht="19.6" spans="1:13">
+    <row r="182" ht="20.25" spans="1:13">
       <c r="A182" s="5" t="s">
         <v>197</v>
       </c>
@@ -9881,7 +9442,7 @@
       </c>
       <c r="M182" s="5"/>
     </row>
-    <row r="183" ht="19.6" spans="1:13">
+    <row r="183" ht="20.25" spans="1:13">
       <c r="A183" s="5" t="s">
         <v>198</v>
       </c>
@@ -9894,7 +9455,7 @@
       </c>
       <c r="M183" s="5"/>
     </row>
-    <row r="184" ht="19.6" spans="1:13">
+    <row r="184" ht="20.25" spans="1:13">
       <c r="A184" s="5" t="s">
         <v>199</v>
       </c>
@@ -9907,7 +9468,7 @@
       </c>
       <c r="M184" s="5"/>
     </row>
-    <row r="185" ht="19.6" spans="1:13">
+    <row r="185" ht="20.25" spans="1:13">
       <c r="A185" s="5" t="s">
         <v>200</v>
       </c>
@@ -9920,7 +9481,7 @@
       </c>
       <c r="M185" s="5"/>
     </row>
-    <row r="186" ht="19.6" spans="1:13">
+    <row r="186" ht="20.25" spans="1:13">
       <c r="A186" s="5" t="s">
         <v>201</v>
       </c>
@@ -9933,7 +9494,7 @@
       </c>
       <c r="M186" s="5"/>
     </row>
-    <row r="187" ht="19.6" spans="1:13">
+    <row r="187" ht="20.25" spans="1:13">
       <c r="A187" s="5" t="s">
         <v>202</v>
       </c>
@@ -9946,7 +9507,7 @@
       </c>
       <c r="M187" s="5"/>
     </row>
-    <row r="188" ht="19.6" spans="1:13">
+    <row r="188" ht="20.25" spans="1:13">
       <c r="A188" s="5" t="s">
         <v>203</v>
       </c>
@@ -9959,7 +9520,7 @@
       </c>
       <c r="M188" s="5"/>
     </row>
-    <row r="189" ht="19.6" spans="1:13">
+    <row r="189" ht="20.25" spans="1:13">
       <c r="A189" s="5" t="s">
         <v>204</v>
       </c>
@@ -9972,7 +9533,7 @@
       </c>
       <c r="M189" s="5"/>
     </row>
-    <row r="190" ht="19.6" spans="1:13">
+    <row r="190" ht="20.25" spans="1:13">
       <c r="A190" s="5" t="s">
         <v>205</v>
       </c>
@@ -9985,7 +9546,7 @@
       </c>
       <c r="M190" s="5"/>
     </row>
-    <row r="191" ht="19.6" spans="1:13">
+    <row r="191" ht="20.25" spans="1:13">
       <c r="A191" s="5" t="s">
         <v>206</v>
       </c>
@@ -9998,7 +9559,7 @@
       </c>
       <c r="M191" s="5"/>
     </row>
-    <row r="192" ht="19.6" spans="1:13">
+    <row r="192" ht="20.25" spans="1:13">
       <c r="A192" s="5" t="s">
         <v>207</v>
       </c>
@@ -10011,7 +9572,7 @@
       </c>
       <c r="M192" s="5"/>
     </row>
-    <row r="193" ht="19.6" spans="1:13">
+    <row r="193" ht="20.25" spans="1:13">
       <c r="A193" s="5" t="s">
         <v>208</v>
       </c>
@@ -10024,7 +9585,7 @@
       </c>
       <c r="M193" s="5"/>
     </row>
-    <row r="194" ht="19.6" spans="1:13">
+    <row r="194" ht="20.25" spans="1:13">
       <c r="A194" s="5" t="s">
         <v>209</v>
       </c>
@@ -10037,7 +9598,7 @@
       </c>
       <c r="M194" s="5"/>
     </row>
-    <row r="195" ht="19.6" spans="1:13">
+    <row r="195" ht="20.25" spans="1:13">
       <c r="A195" s="5" t="s">
         <v>210</v>
       </c>
@@ -10050,7 +9611,7 @@
       </c>
       <c r="M195" s="5"/>
     </row>
-    <row r="196" ht="19.6" spans="1:13">
+    <row r="196" ht="20.25" spans="1:13">
       <c r="A196" s="5" t="s">
         <v>211</v>
       </c>
@@ -10063,7 +9624,7 @@
       </c>
       <c r="M196" s="5"/>
     </row>
-    <row r="197" ht="19.6" spans="1:13">
+    <row r="197" ht="20.25" spans="1:13">
       <c r="A197" s="5" t="s">
         <v>212</v>
       </c>
@@ -10076,7 +9637,7 @@
       </c>
       <c r="M197" s="5"/>
     </row>
-    <row r="198" ht="19.6" spans="1:13">
+    <row r="198" ht="20.25" spans="1:13">
       <c r="A198" s="5" t="s">
         <v>213</v>
       </c>
@@ -10089,7 +9650,7 @@
       </c>
       <c r="M198" s="5"/>
     </row>
-    <row r="199" ht="19.6" spans="1:13">
+    <row r="199" ht="20.25" spans="1:13">
       <c r="A199" s="5" t="s">
         <v>214</v>
       </c>
@@ -10102,7 +9663,7 @@
       </c>
       <c r="M199" s="5"/>
     </row>
-    <row r="200" ht="19.6" spans="1:13">
+    <row r="200" ht="20.25" spans="1:13">
       <c r="A200" s="5" t="s">
         <v>215</v>
       </c>
@@ -10115,7 +9676,7 @@
       </c>
       <c r="M200" s="5"/>
     </row>
-    <row r="201" ht="19.6" spans="1:13">
+    <row r="201" ht="20.25" spans="1:13">
       <c r="A201" s="5" t="s">
         <v>216</v>
       </c>
@@ -10128,7 +9689,7 @@
       </c>
       <c r="M201" s="5"/>
     </row>
-    <row r="202" ht="19.6" spans="1:13">
+    <row r="202" ht="20.25" spans="1:13">
       <c r="A202" s="5" t="s">
         <v>217</v>
       </c>
@@ -10141,7 +9702,7 @@
       </c>
       <c r="M202" s="5"/>
     </row>
-    <row r="203" ht="19.6" spans="1:13">
+    <row r="203" ht="20.25" spans="1:13">
       <c r="A203" s="5" t="s">
         <v>218</v>
       </c>
@@ -10154,7 +9715,7 @@
       </c>
       <c r="M203" s="5"/>
     </row>
-    <row r="204" ht="19.6" spans="1:13">
+    <row r="204" ht="20.25" spans="1:13">
       <c r="A204" s="5" t="s">
         <v>219</v>
       </c>
@@ -10167,7 +9728,7 @@
       </c>
       <c r="M204" s="5"/>
     </row>
-    <row r="205" ht="19.6" spans="1:13">
+    <row r="205" ht="20.25" spans="1:13">
       <c r="A205" s="5" t="s">
         <v>220</v>
       </c>
@@ -10180,7 +9741,7 @@
       </c>
       <c r="M205" s="5"/>
     </row>
-    <row r="206" ht="19.6" spans="1:13">
+    <row r="206" ht="20.25" spans="1:13">
       <c r="A206" s="5" t="s">
         <v>221</v>
       </c>
@@ -10193,7 +9754,7 @@
       </c>
       <c r="M206" s="5"/>
     </row>
-    <row r="207" ht="19.6" spans="1:13">
+    <row r="207" ht="20.25" spans="1:13">
       <c r="A207" s="5" t="s">
         <v>222</v>
       </c>
@@ -10206,7 +9767,7 @@
       </c>
       <c r="M207" s="5"/>
     </row>
-    <row r="208" ht="19.6" spans="1:13">
+    <row r="208" ht="20.25" spans="1:13">
       <c r="A208" s="5" t="s">
         <v>223</v>
       </c>
@@ -10219,7 +9780,7 @@
       </c>
       <c r="M208" s="5"/>
     </row>
-    <row r="209" ht="19.6" spans="1:13">
+    <row r="209" ht="20.25" spans="1:13">
       <c r="A209" s="5" t="s">
         <v>224</v>
       </c>
@@ -10232,7 +9793,7 @@
       </c>
       <c r="M209" s="5"/>
     </row>
-    <row r="210" ht="19.6" spans="1:13">
+    <row r="210" ht="20.25" spans="1:13">
       <c r="A210" s="5" t="s">
         <v>225</v>
       </c>
@@ -10245,7 +9806,7 @@
       </c>
       <c r="M210" s="5"/>
     </row>
-    <row r="211" ht="19.6" spans="1:13">
+    <row r="211" ht="20.25" spans="1:13">
       <c r="A211" s="5" t="s">
         <v>226</v>
       </c>
@@ -10258,7 +9819,7 @@
       </c>
       <c r="M211" s="5"/>
     </row>
-    <row r="212" ht="19.6" spans="1:13">
+    <row r="212" ht="20.25" spans="1:13">
       <c r="A212" s="5" t="s">
         <v>227</v>
       </c>
@@ -10271,7 +9832,7 @@
       </c>
       <c r="M212" s="5"/>
     </row>
-    <row r="213" ht="19.6" spans="1:13">
+    <row r="213" ht="20.25" spans="1:13">
       <c r="A213" s="5" t="s">
         <v>228</v>
       </c>
@@ -10284,7 +9845,7 @@
       </c>
       <c r="M213" s="5"/>
     </row>
-    <row r="214" ht="19.6" spans="1:13">
+    <row r="214" ht="20.25" spans="1:13">
       <c r="A214" s="5" t="s">
         <v>229</v>
       </c>
@@ -10297,7 +9858,7 @@
       </c>
       <c r="M214" s="5"/>
     </row>
-    <row r="215" ht="19.6" spans="1:13">
+    <row r="215" ht="20.25" spans="1:13">
       <c r="A215" s="5" t="s">
         <v>230</v>
       </c>
@@ -10310,7 +9871,7 @@
       </c>
       <c r="M215" s="5"/>
     </row>
-    <row r="216" ht="19.6" spans="1:13">
+    <row r="216" ht="20.25" spans="1:13">
       <c r="A216" s="5" t="s">
         <v>231</v>
       </c>
@@ -10323,7 +9884,7 @@
       </c>
       <c r="M216" s="5"/>
     </row>
-    <row r="217" ht="19.6" spans="1:13">
+    <row r="217" ht="20.25" spans="1:13">
       <c r="A217" s="5" t="s">
         <v>232</v>
       </c>
@@ -10336,7 +9897,7 @@
       </c>
       <c r="M217" s="5"/>
     </row>
-    <row r="218" ht="19.6" spans="1:13">
+    <row r="218" ht="20.25" spans="1:13">
       <c r="A218" s="5" t="s">
         <v>233</v>
       </c>
@@ -10349,7 +9910,7 @@
       </c>
       <c r="M218" s="5"/>
     </row>
-    <row r="219" ht="19.6" spans="1:13">
+    <row r="219" ht="20.25" spans="1:13">
       <c r="A219" s="5" t="s">
         <v>234</v>
       </c>
@@ -10362,7 +9923,7 @@
       </c>
       <c r="M219" s="5"/>
     </row>
-    <row r="220" ht="19.6" spans="1:13">
+    <row r="220" ht="20.25" spans="1:13">
       <c r="A220" s="5" t="s">
         <v>235</v>
       </c>
@@ -10375,7 +9936,7 @@
       </c>
       <c r="M220" s="5"/>
     </row>
-    <row r="221" ht="19.6" spans="1:13">
+    <row r="221" ht="20.25" spans="1:13">
       <c r="A221" s="5" t="s">
         <v>236</v>
       </c>
@@ -10388,7 +9949,7 @@
       </c>
       <c r="M221" s="5"/>
     </row>
-    <row r="222" ht="19.6" spans="1:13">
+    <row r="222" ht="20.25" spans="1:13">
       <c r="A222" s="5" t="s">
         <v>237</v>
       </c>
@@ -10401,7 +9962,7 @@
       </c>
       <c r="M222" s="5"/>
     </row>
-    <row r="223" ht="19.6" spans="1:13">
+    <row r="223" ht="20.25" spans="1:13">
       <c r="A223" s="5" t="s">
         <v>238</v>
       </c>
@@ -10414,7 +9975,7 @@
       </c>
       <c r="M223" s="5"/>
     </row>
-    <row r="224" ht="19.6" spans="1:13">
+    <row r="224" ht="20.25" spans="1:13">
       <c r="A224" s="5" t="s">
         <v>239</v>
       </c>
@@ -10427,7 +9988,7 @@
       </c>
       <c r="M224" s="5"/>
     </row>
-    <row r="225" ht="19.6" spans="1:13">
+    <row r="225" ht="20.25" spans="1:13">
       <c r="A225" s="5" t="s">
         <v>240</v>
       </c>
@@ -10440,7 +10001,7 @@
       </c>
       <c r="M225" s="5"/>
     </row>
-    <row r="226" ht="19.6" spans="1:13">
+    <row r="226" ht="20.25" spans="1:13">
       <c r="A226" s="5" t="s">
         <v>241</v>
       </c>
@@ -10453,7 +10014,7 @@
       </c>
       <c r="M226" s="5"/>
     </row>
-    <row r="227" ht="19.6" spans="1:13">
+    <row r="227" ht="20.25" spans="1:13">
       <c r="A227" s="5" t="s">
         <v>242</v>
       </c>
@@ -10466,7 +10027,7 @@
       </c>
       <c r="M227" s="5"/>
     </row>
-    <row r="228" ht="19.6" spans="1:13">
+    <row r="228" ht="20.25" spans="1:13">
       <c r="A228" s="5" t="s">
         <v>243</v>
       </c>
@@ -10479,7 +10040,7 @@
       </c>
       <c r="M228" s="5"/>
     </row>
-    <row r="229" ht="19.6" spans="1:13">
+    <row r="229" ht="20.25" spans="1:13">
       <c r="A229" s="5" t="s">
         <v>244</v>
       </c>
@@ -10492,7 +10053,7 @@
       </c>
       <c r="M229" s="5"/>
     </row>
-    <row r="230" ht="19.6" spans="1:13">
+    <row r="230" ht="20.25" spans="1:13">
       <c r="A230" s="5" t="s">
         <v>245</v>
       </c>
@@ -10505,7 +10066,7 @@
       </c>
       <c r="M230" s="5"/>
     </row>
-    <row r="231" ht="19.6" spans="1:13">
+    <row r="231" ht="20.25" spans="1:13">
       <c r="A231" s="5" t="s">
         <v>246</v>
       </c>
@@ -10518,7 +10079,7 @@
       </c>
       <c r="M231" s="5"/>
     </row>
-    <row r="232" ht="19.6" spans="1:13">
+    <row r="232" ht="20.25" spans="1:13">
       <c r="A232" s="5" t="s">
         <v>247</v>
       </c>
@@ -10531,7 +10092,7 @@
       </c>
       <c r="M232" s="5"/>
     </row>
-    <row r="233" ht="19.6" spans="1:13">
+    <row r="233" ht="20.25" spans="1:13">
       <c r="A233" s="5" t="s">
         <v>248</v>
       </c>
@@ -10544,7 +10105,7 @@
       </c>
       <c r="M233" s="5"/>
     </row>
-    <row r="234" ht="19.6" spans="1:13">
+    <row r="234" ht="20.25" spans="1:13">
       <c r="A234" s="5" t="s">
         <v>249</v>
       </c>
@@ -10557,7 +10118,7 @@
       </c>
       <c r="M234" s="5"/>
     </row>
-    <row r="235" ht="19.6" spans="1:13">
+    <row r="235" ht="20.25" spans="1:13">
       <c r="A235" s="5" t="s">
         <v>250</v>
       </c>
@@ -10570,7 +10131,7 @@
       </c>
       <c r="M235" s="5"/>
     </row>
-    <row r="236" ht="19.6" spans="1:13">
+    <row r="236" ht="20.25" spans="1:13">
       <c r="A236" s="5" t="s">
         <v>251</v>
       </c>
@@ -10583,7 +10144,7 @@
       </c>
       <c r="M236" s="5"/>
     </row>
-    <row r="237" ht="19.6" spans="1:13">
+    <row r="237" ht="20.25" spans="1:13">
       <c r="A237" s="5" t="s">
         <v>252</v>
       </c>
@@ -10596,7 +10157,7 @@
       </c>
       <c r="M237" s="5"/>
     </row>
-    <row r="238" ht="19.6" spans="1:13">
+    <row r="238" ht="20.25" spans="1:13">
       <c r="A238" s="5" t="s">
         <v>253</v>
       </c>
@@ -10609,7 +10170,7 @@
       </c>
       <c r="M238" s="5"/>
     </row>
-    <row r="239" ht="19.6" spans="1:13">
+    <row r="239" ht="20.25" spans="1:13">
       <c r="A239" s="5" t="s">
         <v>254</v>
       </c>
@@ -10622,7 +10183,7 @@
       </c>
       <c r="M239" s="5"/>
     </row>
-    <row r="240" ht="19.6" spans="1:13">
+    <row r="240" ht="20.25" spans="1:13">
       <c r="A240" s="5" t="s">
         <v>255</v>
       </c>
@@ -10635,7 +10196,7 @@
       </c>
       <c r="M240" s="5"/>
     </row>
-    <row r="241" ht="19.6" spans="1:13">
+    <row r="241" ht="20.25" spans="1:13">
       <c r="A241" s="5" t="s">
         <v>256</v>
       </c>
@@ -10648,7 +10209,7 @@
       </c>
       <c r="M241" s="5"/>
     </row>
-    <row r="242" ht="19.6" spans="1:13">
+    <row r="242" ht="20.25" spans="1:13">
       <c r="A242" s="5" t="s">
         <v>257</v>
       </c>
@@ -10661,7 +10222,7 @@
       </c>
       <c r="M242" s="5"/>
     </row>
-    <row r="243" ht="19.6" spans="1:13">
+    <row r="243" ht="20.25" spans="1:13">
       <c r="A243" s="5" t="s">
         <v>258</v>
       </c>
@@ -10674,7 +10235,7 @@
       </c>
       <c r="M243" s="5"/>
     </row>
-    <row r="244" ht="19.6" spans="1:13">
+    <row r="244" ht="20.25" spans="1:13">
       <c r="A244" s="5" t="s">
         <v>259</v>
       </c>
@@ -10687,7 +10248,7 @@
       </c>
       <c r="M244" s="5"/>
     </row>
-    <row r="245" ht="19.6" spans="1:13">
+    <row r="245" ht="20.25" spans="1:13">
       <c r="A245" s="5" t="s">
         <v>260</v>
       </c>
@@ -10700,7 +10261,7 @@
       </c>
       <c r="M245" s="5"/>
     </row>
-    <row r="246" ht="19.6" spans="1:13">
+    <row r="246" ht="20.25" spans="1:13">
       <c r="A246" s="5" t="s">
         <v>261</v>
       </c>
@@ -10713,7 +10274,7 @@
       </c>
       <c r="M246" s="5"/>
     </row>
-    <row r="247" ht="19.6" spans="1:13">
+    <row r="247" ht="20.25" spans="1:13">
       <c r="A247" s="5" t="s">
         <v>262</v>
       </c>
@@ -10726,7 +10287,7 @@
       </c>
       <c r="M247" s="5"/>
     </row>
-    <row r="248" ht="19.6" spans="1:13">
+    <row r="248" ht="20.25" spans="1:13">
       <c r="A248" s="5" t="s">
         <v>263</v>
       </c>
@@ -10739,7 +10300,7 @@
       </c>
       <c r="M248" s="5"/>
     </row>
-    <row r="249" ht="19.6" spans="1:13">
+    <row r="249" ht="20.25" spans="1:13">
       <c r="A249" s="5" t="s">
         <v>264</v>
       </c>
@@ -10752,7 +10313,7 @@
       </c>
       <c r="M249" s="5"/>
     </row>
-    <row r="250" ht="19.6" spans="1:13">
+    <row r="250" ht="20.25" spans="1:13">
       <c r="A250" s="5" t="s">
         <v>265</v>
       </c>
@@ -10765,7 +10326,7 @@
       </c>
       <c r="M250" s="5"/>
     </row>
-    <row r="251" ht="19.6" spans="1:13">
+    <row r="251" ht="20.25" spans="1:13">
       <c r="A251" s="5" t="s">
         <v>266</v>
       </c>
@@ -10778,7 +10339,7 @@
       </c>
       <c r="M251" s="5"/>
     </row>
-    <row r="252" ht="19.6" spans="1:13">
+    <row r="252" ht="20.25" spans="1:13">
       <c r="A252" s="5" t="s">
         <v>267</v>
       </c>
@@ -10791,7 +10352,7 @@
       </c>
       <c r="M252" s="5"/>
     </row>
-    <row r="253" ht="19.6" spans="1:13">
+    <row r="253" ht="20.25" spans="1:13">
       <c r="A253" s="5" t="s">
         <v>268</v>
       </c>
@@ -10804,7 +10365,7 @@
       </c>
       <c r="M253" s="5"/>
     </row>
-    <row r="254" ht="19.6" spans="1:13">
+    <row r="254" ht="20.25" spans="1:13">
       <c r="A254" s="5" t="s">
         <v>269</v>
       </c>
@@ -10817,7 +10378,7 @@
       </c>
       <c r="M254" s="5"/>
     </row>
-    <row r="255" ht="19.6" spans="1:13">
+    <row r="255" ht="20.25" spans="1:13">
       <c r="A255" s="5" t="s">
         <v>270</v>
       </c>
@@ -10830,7 +10391,7 @@
       </c>
       <c r="M255" s="5"/>
     </row>
-    <row r="256" ht="19.6" spans="1:13">
+    <row r="256" ht="20.25" spans="1:13">
       <c r="A256" s="5" t="s">
         <v>271</v>
       </c>
@@ -10843,7 +10404,7 @@
       </c>
       <c r="M256" s="5"/>
     </row>
-    <row r="257" ht="19.6" spans="1:13">
+    <row r="257" ht="20.25" spans="1:13">
       <c r="A257" s="5" t="s">
         <v>272</v>
       </c>
@@ -10856,7 +10417,7 @@
       </c>
       <c r="M257" s="5"/>
     </row>
-    <row r="258" ht="19.6" spans="1:13">
+    <row r="258" ht="20.25" spans="1:13">
       <c r="A258" s="5" t="s">
         <v>273</v>
       </c>
@@ -10869,7 +10430,7 @@
       </c>
       <c r="M258" s="5"/>
     </row>
-    <row r="259" ht="19.6" spans="1:13">
+    <row r="259" ht="20.25" spans="1:13">
       <c r="A259" s="5" t="s">
         <v>274</v>
       </c>
@@ -10882,7 +10443,7 @@
       </c>
       <c r="M259" s="5"/>
     </row>
-    <row r="260" ht="19.6" spans="1:13">
+    <row r="260" ht="20.25" spans="1:13">
       <c r="A260" s="5" t="s">
         <v>275</v>
       </c>
@@ -10895,7 +10456,7 @@
       </c>
       <c r="M260" s="5"/>
     </row>
-    <row r="261" ht="19.6" spans="1:13">
+    <row r="261" ht="20.25" spans="1:13">
       <c r="A261" s="5" t="s">
         <v>276</v>
       </c>
@@ -10908,7 +10469,7 @@
       </c>
       <c r="M261" s="5"/>
     </row>
-    <row r="262" ht="19.6" spans="1:13">
+    <row r="262" ht="20.25" spans="1:13">
       <c r="A262" s="5" t="s">
         <v>277</v>
       </c>
@@ -10921,7 +10482,7 @@
       </c>
       <c r="M262" s="5"/>
     </row>
-    <row r="263" ht="19.6" spans="1:13">
+    <row r="263" ht="20.25" spans="1:13">
       <c r="A263" s="5" t="s">
         <v>278</v>
       </c>
@@ -10934,7 +10495,7 @@
       </c>
       <c r="M263" s="5"/>
     </row>
-    <row r="264" ht="19.6" spans="1:13">
+    <row r="264" ht="20.25" spans="1:13">
       <c r="A264" s="5" t="s">
         <v>279</v>
       </c>
@@ -10947,7 +10508,7 @@
       </c>
       <c r="M264" s="5"/>
     </row>
-    <row r="265" ht="19.6" spans="1:13">
+    <row r="265" ht="20.25" spans="1:13">
       <c r="A265" s="5" t="s">
         <v>280</v>
       </c>
@@ -10960,7 +10521,7 @@
       </c>
       <c r="M265" s="5"/>
     </row>
-    <row r="266" ht="19.6" spans="1:13">
+    <row r="266" ht="20.25" spans="1:13">
       <c r="A266" s="5" t="s">
         <v>281</v>
       </c>
@@ -10973,7 +10534,7 @@
       </c>
       <c r="M266" s="5"/>
     </row>
-    <row r="267" ht="19.6" spans="1:13">
+    <row r="267" ht="20.25" spans="1:13">
       <c r="A267" s="5" t="s">
         <v>282</v>
       </c>
@@ -10986,7 +10547,7 @@
       </c>
       <c r="M267" s="5"/>
     </row>
-    <row r="268" ht="19.6" spans="1:13">
+    <row r="268" ht="20.25" spans="1:13">
       <c r="A268" s="5" t="s">
         <v>283</v>
       </c>
@@ -10999,7 +10560,7 @@
       </c>
       <c r="M268" s="5"/>
     </row>
-    <row r="269" ht="19.6" spans="1:13">
+    <row r="269" ht="20.25" spans="1:13">
       <c r="A269" s="5" t="s">
         <v>284</v>
       </c>
@@ -11012,7 +10573,7 @@
       </c>
       <c r="M269" s="5"/>
     </row>
-    <row r="270" ht="19.6" spans="1:13">
+    <row r="270" ht="20.25" spans="1:13">
       <c r="A270" s="5" t="s">
         <v>285</v>
       </c>
@@ -11025,7 +10586,7 @@
       </c>
       <c r="M270" s="5"/>
     </row>
-    <row r="271" ht="19.6" spans="1:13">
+    <row r="271" ht="20.25" spans="1:13">
       <c r="A271" s="5" t="s">
         <v>286</v>
       </c>
@@ -11038,7 +10599,7 @@
       </c>
       <c r="M271" s="5"/>
     </row>
-    <row r="272" ht="19.6" spans="1:13">
+    <row r="272" ht="20.25" spans="1:13">
       <c r="A272" s="5" t="s">
         <v>287</v>
       </c>
@@ -11051,7 +10612,7 @@
       </c>
       <c r="M272" s="5"/>
     </row>
-    <row r="273" ht="19.6" spans="1:13">
+    <row r="273" ht="20.25" spans="1:13">
       <c r="A273" s="5" t="s">
         <v>288</v>
       </c>
@@ -11064,7 +10625,7 @@
       </c>
       <c r="M273" s="5"/>
     </row>
-    <row r="274" ht="19.6" spans="1:13">
+    <row r="274" ht="20.25" spans="1:13">
       <c r="A274" s="5" t="s">
         <v>289</v>
       </c>
@@ -11077,7 +10638,7 @@
       </c>
       <c r="M274" s="5"/>
     </row>
-    <row r="275" ht="19.6" spans="1:13">
+    <row r="275" ht="20.25" spans="1:13">
       <c r="A275" s="5" t="s">
         <v>290</v>
       </c>
@@ -11090,7 +10651,7 @@
       </c>
       <c r="M275" s="5"/>
     </row>
-    <row r="276" ht="19.6" spans="1:13">
+    <row r="276" ht="20.25" spans="1:13">
       <c r="A276" s="5" t="s">
         <v>291</v>
       </c>
@@ -11103,7 +10664,7 @@
       </c>
       <c r="M276" s="5"/>
     </row>
-    <row r="277" ht="19.6" spans="1:13">
+    <row r="277" ht="20.25" spans="1:13">
       <c r="A277" s="5" t="s">
         <v>292</v>
       </c>
@@ -11116,7 +10677,7 @@
       </c>
       <c r="M277" s="5"/>
     </row>
-    <row r="278" ht="19.6" spans="1:13">
+    <row r="278" ht="20.25" spans="1:13">
       <c r="A278" s="5" t="s">
         <v>293</v>
       </c>
@@ -11129,7 +10690,7 @@
       </c>
       <c r="M278" s="5"/>
     </row>
-    <row r="279" ht="19.6" spans="1:13">
+    <row r="279" ht="20.25" spans="1:13">
       <c r="A279" s="5" t="s">
         <v>294</v>
       </c>
@@ -11142,7 +10703,7 @@
       </c>
       <c r="M279" s="5"/>
     </row>
-    <row r="280" ht="19.6" spans="1:13">
+    <row r="280" ht="20.25" spans="1:13">
       <c r="A280" s="5" t="s">
         <v>295</v>
       </c>
@@ -11155,7 +10716,7 @@
       </c>
       <c r="M280" s="5"/>
     </row>
-    <row r="281" ht="19.6" spans="1:13">
+    <row r="281" ht="20.25" spans="1:13">
       <c r="A281" s="5" t="s">
         <v>296</v>
       </c>
@@ -11168,7 +10729,7 @@
       </c>
       <c r="M281" s="5"/>
     </row>
-    <row r="282" ht="19.6" spans="1:13">
+    <row r="282" ht="20.25" spans="1:13">
       <c r="A282" s="5" t="s">
         <v>297</v>
       </c>
@@ -11181,7 +10742,7 @@
       </c>
       <c r="M282" s="5"/>
     </row>
-    <row r="283" ht="19.6" spans="1:13">
+    <row r="283" ht="20.25" spans="1:13">
       <c r="A283" s="5" t="s">
         <v>298</v>
       </c>
@@ -11194,7 +10755,7 @@
       </c>
       <c r="M283" s="5"/>
     </row>
-    <row r="284" ht="19.6" spans="1:13">
+    <row r="284" ht="20.25" spans="1:13">
       <c r="A284" s="5" t="s">
         <v>299</v>
       </c>
@@ -11207,7 +10768,7 @@
       </c>
       <c r="M284" s="5"/>
     </row>
-    <row r="285" ht="19.6" spans="1:13">
+    <row r="285" ht="20.25" spans="1:13">
       <c r="A285" s="5" t="s">
         <v>300</v>
       </c>
@@ -11220,7 +10781,7 @@
       </c>
       <c r="M285" s="5"/>
     </row>
-    <row r="286" ht="19.6" spans="1:13">
+    <row r="286" ht="20.25" spans="1:13">
       <c r="A286" s="5" t="s">
         <v>301</v>
       </c>
@@ -11233,7 +10794,7 @@
       </c>
       <c r="M286" s="5"/>
     </row>
-    <row r="287" ht="19.6" spans="1:13">
+    <row r="287" ht="20.25" spans="1:13">
       <c r="A287" s="5" t="s">
         <v>302</v>
       </c>
@@ -11246,7 +10807,7 @@
       </c>
       <c r="M287" s="5"/>
     </row>
-    <row r="288" ht="19.6" spans="1:13">
+    <row r="288" ht="20.25" spans="1:13">
       <c r="A288" s="5" t="s">
         <v>303</v>
       </c>
@@ -11259,7 +10820,7 @@
       </c>
       <c r="M288" s="5"/>
     </row>
-    <row r="289" ht="19.6" spans="1:13">
+    <row r="289" ht="20.25" spans="1:13">
       <c r="A289" s="5" t="s">
         <v>304</v>
       </c>
@@ -11272,7 +10833,7 @@
       </c>
       <c r="M289" s="5"/>
     </row>
-    <row r="290" ht="19.6" spans="1:13">
+    <row r="290" ht="20.25" spans="1:13">
       <c r="A290" s="5" t="s">
         <v>305</v>
       </c>
@@ -11285,7 +10846,7 @@
       </c>
       <c r="M290" s="5"/>
     </row>
-    <row r="291" ht="19.6" spans="1:13">
+    <row r="291" ht="20.25" spans="1:13">
       <c r="A291" s="5" t="s">
         <v>306</v>
       </c>
@@ -11298,7 +10859,7 @@
       </c>
       <c r="M291" s="5"/>
     </row>
-    <row r="292" ht="19.6" spans="1:13">
+    <row r="292" ht="20.25" spans="1:13">
       <c r="A292" s="5" t="s">
         <v>307</v>
       </c>
@@ -11311,7 +10872,7 @@
       </c>
       <c r="M292" s="5"/>
     </row>
-    <row r="293" ht="19.6" spans="1:13">
+    <row r="293" ht="20.25" spans="1:13">
       <c r="A293" s="5" t="s">
         <v>308</v>
       </c>
@@ -11324,7 +10885,7 @@
       </c>
       <c r="M293" s="5"/>
     </row>
-    <row r="294" ht="19.6" spans="1:13">
+    <row r="294" ht="20.25" spans="1:13">
       <c r="A294" s="5" t="s">
         <v>309</v>
       </c>
@@ -11337,7 +10898,7 @@
       </c>
       <c r="M294" s="5"/>
     </row>
-    <row r="295" ht="19.6" spans="1:13">
+    <row r="295" ht="20.25" spans="1:13">
       <c r="A295" s="5" t="s">
         <v>310</v>
       </c>
@@ -11350,7 +10911,7 @@
       </c>
       <c r="M295" s="5"/>
     </row>
-    <row r="296" ht="19.6" spans="1:13">
+    <row r="296" ht="20.25" spans="1:13">
       <c r="A296" s="5" t="s">
         <v>311</v>
       </c>
@@ -11363,7 +10924,7 @@
       </c>
       <c r="M296" s="5"/>
     </row>
-    <row r="297" ht="19.6" spans="1:13">
+    <row r="297" ht="20.25" spans="1:13">
       <c r="A297" s="5" t="s">
         <v>312</v>
       </c>
@@ -11376,7 +10937,7 @@
       </c>
       <c r="M297" s="5"/>
     </row>
-    <row r="298" ht="19.6" spans="1:13">
+    <row r="298" ht="20.25" spans="1:13">
       <c r="A298" s="5" t="s">
         <v>313</v>
       </c>
@@ -11389,7 +10950,7 @@
       </c>
       <c r="M298" s="5"/>
     </row>
-    <row r="299" ht="19.6" spans="1:13">
+    <row r="299" ht="20.25" spans="1:13">
       <c r="A299" s="5" t="s">
         <v>314</v>
       </c>
@@ -11402,7 +10963,7 @@
       </c>
       <c r="M299" s="5"/>
     </row>
-    <row r="300" ht="19.6" spans="1:13">
+    <row r="300" ht="20.25" spans="1:13">
       <c r="A300" s="5" t="s">
         <v>315</v>
       </c>
@@ -11415,7 +10976,7 @@
       </c>
       <c r="M300" s="5"/>
     </row>
-    <row r="301" ht="19.6" spans="1:13">
+    <row r="301" ht="20.25" spans="1:13">
       <c r="A301" s="5" t="s">
         <v>316</v>
       </c>
@@ -11428,7 +10989,7 @@
       </c>
       <c r="M301" s="5"/>
     </row>
-    <row r="302" ht="19.6" spans="1:13">
+    <row r="302" ht="20.25" spans="1:13">
       <c r="A302" s="5" t="s">
         <v>317</v>
       </c>
@@ -11441,7 +11002,7 @@
       </c>
       <c r="M302" s="5"/>
     </row>
-    <row r="303" ht="19.6" spans="1:13">
+    <row r="303" ht="20.25" spans="1:13">
       <c r="A303" s="5" t="s">
         <v>318</v>
       </c>
@@ -11454,7 +11015,7 @@
       </c>
       <c r="M303" s="5"/>
     </row>
-    <row r="304" ht="19.6" spans="1:13">
+    <row r="304" ht="20.25" spans="1:13">
       <c r="A304" s="5" t="s">
         <v>319</v>
       </c>
@@ -11467,7 +11028,7 @@
       </c>
       <c r="M304" s="5"/>
     </row>
-    <row r="305" ht="19.6" spans="1:13">
+    <row r="305" ht="20.25" spans="1:13">
       <c r="A305" s="5" t="s">
         <v>320</v>
       </c>
@@ -11480,7 +11041,7 @@
       </c>
       <c r="M305" s="5"/>
     </row>
-    <row r="306" ht="19.6" spans="1:13">
+    <row r="306" ht="20.25" spans="1:13">
       <c r="A306" s="5" t="s">
         <v>321</v>
       </c>
@@ -11493,7 +11054,7 @@
       </c>
       <c r="M306" s="5"/>
     </row>
-    <row r="307" ht="19.6" spans="1:13">
+    <row r="307" ht="20.25" spans="1:13">
       <c r="A307" s="5" t="s">
         <v>322</v>
       </c>
@@ -11506,7 +11067,7 @@
       </c>
       <c r="M307" s="5"/>
     </row>
-    <row r="308" ht="19.6" spans="1:13">
+    <row r="308" ht="20.25" spans="1:13">
       <c r="A308" s="5" t="s">
         <v>323</v>
       </c>
@@ -11519,7 +11080,7 @@
       </c>
       <c r="M308" s="5"/>
     </row>
-    <row r="309" ht="19.6" spans="1:13">
+    <row r="309" ht="20.25" spans="1:13">
       <c r="A309" s="5" t="s">
         <v>324</v>
       </c>
@@ -11532,7 +11093,7 @@
       </c>
       <c r="M309" s="5"/>
     </row>
-    <row r="310" ht="19.6" spans="1:13">
+    <row r="310" ht="20.25" spans="1:13">
       <c r="A310" s="5" t="s">
         <v>325</v>
       </c>
@@ -11545,7 +11106,7 @@
       </c>
       <c r="M310" s="5"/>
     </row>
-    <row r="311" ht="19.6" spans="1:13">
+    <row r="311" ht="20.25" spans="1:13">
       <c r="A311" s="5" t="s">
         <v>326</v>
       </c>
@@ -11558,7 +11119,7 @@
       </c>
       <c r="M311" s="5"/>
     </row>
-    <row r="312" ht="19.6" spans="1:13">
+    <row r="312" ht="20.25" spans="1:13">
       <c r="A312" s="5" t="s">
         <v>327</v>
       </c>
@@ -11571,7 +11132,7 @@
       </c>
       <c r="M312" s="5"/>
     </row>
-    <row r="313" ht="19.6" spans="1:13">
+    <row r="313" ht="20.25" spans="1:13">
       <c r="A313" s="5" t="s">
         <v>328</v>
       </c>
@@ -11584,7 +11145,7 @@
       </c>
       <c r="M313" s="5"/>
     </row>
-    <row r="314" ht="19.6" spans="1:13">
+    <row r="314" ht="20.25" spans="1:13">
       <c r="A314" s="5" t="s">
         <v>329</v>
       </c>
@@ -11597,7 +11158,7 @@
       </c>
       <c r="M314" s="5"/>
     </row>
-    <row r="315" ht="19.6" spans="1:13">
+    <row r="315" ht="20.25" spans="1:13">
       <c r="A315" s="5" t="s">
         <v>330</v>
       </c>
@@ -11610,7 +11171,7 @@
       </c>
       <c r="M315" s="5"/>
     </row>
-    <row r="316" ht="19.6" spans="1:13">
+    <row r="316" ht="20.25" spans="1:13">
       <c r="A316" s="5" t="s">
         <v>331</v>
       </c>
@@ -11623,7 +11184,7 @@
       </c>
       <c r="M316" s="5"/>
     </row>
-    <row r="317" ht="19.6" spans="1:13">
+    <row r="317" ht="20.25" spans="1:13">
       <c r="A317" s="5" t="s">
         <v>332</v>
       </c>
@@ -11636,7 +11197,7 @@
       </c>
       <c r="M317" s="5"/>
     </row>
-    <row r="318" ht="19.6" spans="1:13">
+    <row r="318" ht="20.25" spans="1:13">
       <c r="A318" s="5" t="s">
         <v>333</v>
       </c>
@@ -11649,7 +11210,7 @@
       </c>
       <c r="M318" s="5"/>
     </row>
-    <row r="319" ht="19.6" spans="1:13">
+    <row r="319" ht="20.25" spans="1:13">
       <c r="A319" s="5" t="s">
         <v>334</v>
       </c>
@@ -11662,7 +11223,7 @@
       </c>
       <c r="M319" s="5"/>
     </row>
-    <row r="320" ht="19.6" spans="1:13">
+    <row r="320" ht="20.25" spans="1:13">
       <c r="A320" s="5" t="s">
         <v>335</v>
       </c>
@@ -11675,7 +11236,7 @@
       </c>
       <c r="M320" s="5"/>
     </row>
-    <row r="321" ht="19.6" spans="1:13">
+    <row r="321" ht="20.25" spans="1:13">
       <c r="A321" s="5" t="s">
         <v>336</v>
       </c>
@@ -11688,7 +11249,7 @@
       </c>
       <c r="M321" s="5"/>
     </row>
-    <row r="322" ht="19.6" spans="1:13">
+    <row r="322" ht="20.25" spans="1:13">
       <c r="A322" s="5" t="s">
         <v>337</v>
       </c>
@@ -11701,7 +11262,7 @@
       </c>
       <c r="M322" s="5"/>
     </row>
-    <row r="323" ht="19.6" spans="1:13">
+    <row r="323" ht="20.25" spans="1:13">
       <c r="A323" s="5" t="s">
         <v>338</v>
       </c>
@@ -11714,7 +11275,7 @@
       </c>
       <c r="M323" s="5"/>
     </row>
-    <row r="324" ht="19.6" spans="1:13">
+    <row r="324" ht="20.25" spans="1:13">
       <c r="A324" s="5" t="s">
         <v>339</v>
       </c>
@@ -11727,7 +11288,7 @@
       </c>
       <c r="M324" s="5"/>
     </row>
-    <row r="325" ht="19.6" spans="1:13">
+    <row r="325" ht="20.25" spans="1:13">
       <c r="A325" s="5" t="s">
         <v>340</v>
       </c>
@@ -11740,7 +11301,7 @@
       </c>
       <c r="M325" s="5"/>
     </row>
-    <row r="326" ht="19.6" spans="1:13">
+    <row r="326" ht="20.25" spans="1:13">
       <c r="A326" s="5" t="s">
         <v>341</v>
       </c>
@@ -11753,7 +11314,7 @@
       </c>
       <c r="M326" s="5"/>
     </row>
-    <row r="327" ht="19.6" spans="1:13">
+    <row r="327" ht="20.25" spans="1:13">
       <c r="A327" s="5" t="s">
         <v>342</v>
       </c>
@@ -11766,7 +11327,7 @@
       </c>
       <c r="M327" s="5"/>
     </row>
-    <row r="328" ht="19.6" spans="1:13">
+    <row r="328" ht="20.25" spans="1:13">
       <c r="A328" s="5" t="s">
         <v>343</v>
       </c>
@@ -11779,7 +11340,7 @@
       </c>
       <c r="M328" s="5"/>
     </row>
-    <row r="329" ht="19.6" spans="1:13">
+    <row r="329" ht="20.25" spans="1:13">
       <c r="A329" s="5" t="s">
         <v>344</v>
       </c>
@@ -11792,7 +11353,7 @@
       </c>
       <c r="M329" s="5"/>
     </row>
-    <row r="330" ht="19.6" spans="1:13">
+    <row r="330" ht="20.25" spans="1:13">
       <c r="A330" s="5" t="s">
         <v>345</v>
       </c>
@@ -11805,7 +11366,7 @@
       </c>
       <c r="M330" s="5"/>
     </row>
-    <row r="331" ht="19.6" spans="1:13">
+    <row r="331" ht="20.25" spans="1:13">
       <c r="A331" s="5" t="s">
         <v>346</v>
       </c>
@@ -11818,7 +11379,7 @@
       </c>
       <c r="M331" s="5"/>
     </row>
-    <row r="332" ht="19.6" spans="1:13">
+    <row r="332" ht="20.25" spans="1:13">
       <c r="A332" s="5" t="s">
         <v>347</v>
       </c>
@@ -11831,7 +11392,7 @@
       </c>
       <c r="M332" s="5"/>
     </row>
-    <row r="333" ht="19.6" spans="1:13">
+    <row r="333" ht="20.25" spans="1:13">
       <c r="A333" s="5" t="s">
         <v>348</v>
       </c>
@@ -11844,7 +11405,7 @@
       </c>
       <c r="M333" s="5"/>
     </row>
-    <row r="334" ht="19.6" spans="1:13">
+    <row r="334" ht="20.25" spans="1:13">
       <c r="A334" s="5" t="s">
         <v>349</v>
       </c>
@@ -11857,7 +11418,7 @@
       </c>
       <c r="M334" s="5"/>
     </row>
-    <row r="335" ht="19.6" spans="1:13">
+    <row r="335" ht="20.25" spans="1:13">
       <c r="A335" s="5" t="s">
         <v>350</v>
       </c>
@@ -11870,7 +11431,7 @@
       </c>
       <c r="M335" s="5"/>
     </row>
-    <row r="336" ht="19.6" spans="1:13">
+    <row r="336" ht="20.25" spans="1:13">
       <c r="A336" s="5" t="s">
         <v>351</v>
       </c>
@@ -11883,7 +11444,7 @@
       </c>
       <c r="M336" s="5"/>
     </row>
-    <row r="337" ht="19.6" spans="1:13">
+    <row r="337" ht="20.25" spans="1:13">
       <c r="A337" s="5" t="s">
         <v>352</v>
       </c>
@@ -11896,7 +11457,7 @@
       </c>
       <c r="M337" s="5"/>
     </row>
-    <row r="338" ht="19.6" spans="1:13">
+    <row r="338" ht="20.25" spans="1:13">
       <c r="A338" s="5" t="s">
         <v>353</v>
       </c>
@@ -11909,7 +11470,7 @@
       </c>
       <c r="M338" s="5"/>
     </row>
-    <row r="339" ht="19.6" spans="1:13">
+    <row r="339" ht="20.25" spans="1:13">
       <c r="A339" s="5" t="s">
         <v>354</v>
       </c>
@@ -11922,7 +11483,7 @@
       </c>
       <c r="M339" s="5"/>
     </row>
-    <row r="340" ht="19.6" spans="1:13">
+    <row r="340" ht="20.25" spans="1:13">
       <c r="A340" s="5" t="s">
         <v>355</v>
       </c>
@@ -11935,7 +11496,7 @@
       </c>
       <c r="M340" s="5"/>
     </row>
-    <row r="341" ht="19.6" spans="1:13">
+    <row r="341" ht="20.25" spans="1:13">
       <c r="A341" s="5" t="s">
         <v>356</v>
       </c>
@@ -11948,7 +11509,7 @@
       </c>
       <c r="M341" s="5"/>
     </row>
-    <row r="342" ht="19.6" spans="1:13">
+    <row r="342" ht="20.25" spans="1:13">
       <c r="A342" s="5" t="s">
         <v>357</v>
       </c>
@@ -11961,7 +11522,7 @@
       </c>
       <c r="M342" s="5"/>
     </row>
-    <row r="343" ht="19.6" spans="1:13">
+    <row r="343" ht="20.25" spans="1:13">
       <c r="A343" s="5" t="s">
         <v>358</v>
       </c>
@@ -11974,7 +11535,7 @@
       </c>
       <c r="M343" s="5"/>
     </row>
-    <row r="344" ht="19.6" spans="1:13">
+    <row r="344" ht="20.25" spans="1:13">
       <c r="A344" s="5" t="s">
         <v>359</v>
       </c>
@@ -11987,7 +11548,7 @@
       </c>
       <c r="M344" s="5"/>
     </row>
-    <row r="345" ht="19.6" spans="1:13">
+    <row r="345" ht="20.25" spans="1:13">
       <c r="A345" s="5" t="s">
         <v>360</v>
       </c>
@@ -12000,7 +11561,7 @@
       </c>
       <c r="M345" s="5"/>
     </row>
-    <row r="346" ht="19.6" spans="1:13">
+    <row r="346" ht="20.25" spans="1:13">
       <c r="A346" s="5" t="s">
         <v>361</v>
       </c>
@@ -12013,7 +11574,7 @@
       </c>
       <c r="M346" s="5"/>
     </row>
-    <row r="347" ht="19.6" spans="1:13">
+    <row r="347" ht="20.25" spans="1:13">
       <c r="A347" s="5" t="s">
         <v>362</v>
       </c>
@@ -12026,7 +11587,7 @@
       </c>
       <c r="M347" s="5"/>
     </row>
-    <row r="348" ht="19.6" spans="1:13">
+    <row r="348" ht="20.25" spans="1:13">
       <c r="A348" s="5" t="s">
         <v>363</v>
       </c>
@@ -12039,7 +11600,7 @@
       </c>
       <c r="M348" s="5"/>
     </row>
-    <row r="349" ht="19.6" spans="1:13">
+    <row r="349" ht="20.25" spans="1:13">
       <c r="A349" s="5" t="s">
         <v>364</v>
       </c>
@@ -12052,7 +11613,7 @@
       </c>
       <c r="M349" s="5"/>
     </row>
-    <row r="350" ht="19.6" spans="1:13">
+    <row r="350" ht="20.25" spans="1:13">
       <c r="A350" s="5" t="s">
         <v>365</v>
       </c>
@@ -12065,7 +11626,7 @@
       </c>
       <c r="M350" s="5"/>
     </row>
-    <row r="351" ht="19.6" spans="1:13">
+    <row r="351" ht="20.25" spans="1:13">
       <c r="A351" s="5" t="s">
         <v>366</v>
       </c>
@@ -12078,7 +11639,7 @@
       </c>
       <c r="M351" s="5"/>
     </row>
-    <row r="352" ht="19.6" spans="1:13">
+    <row r="352" ht="20.25" spans="1:13">
       <c r="A352" s="5" t="s">
         <v>367</v>
       </c>
@@ -12091,7 +11652,7 @@
       </c>
       <c r="M352" s="5"/>
     </row>
-    <row r="353" ht="19.6" spans="1:13">
+    <row r="353" ht="20.25" spans="1:13">
       <c r="A353" s="5" t="s">
         <v>368</v>
       </c>
@@ -12104,7 +11665,7 @@
       </c>
       <c r="M353" s="5"/>
     </row>
-    <row r="354" ht="19.6" spans="1:13">
+    <row r="354" ht="20.25" spans="1:13">
       <c r="A354" s="5" t="s">
         <v>369</v>
       </c>
@@ -12117,7 +11678,7 @@
       </c>
       <c r="M354" s="5"/>
     </row>
-    <row r="355" ht="19.6" spans="1:13">
+    <row r="355" ht="20.25" spans="1:13">
       <c r="A355" s="5" t="s">
         <v>370</v>
       </c>
@@ -12130,7 +11691,7 @@
       </c>
       <c r="M355" s="5"/>
     </row>
-    <row r="356" ht="19.6" spans="1:13">
+    <row r="356" ht="20.25" spans="1:13">
       <c r="A356" s="5" t="s">
         <v>371</v>
       </c>
@@ -12143,7 +11704,7 @@
       </c>
       <c r="M356" s="5"/>
     </row>
-    <row r="357" ht="19.6" spans="1:13">
+    <row r="357" ht="20.25" spans="1:13">
       <c r="A357" s="5" t="s">
         <v>372</v>
       </c>
@@ -12156,7 +11717,7 @@
       </c>
       <c r="M357" s="5"/>
     </row>
-    <row r="358" ht="19.6" spans="1:13">
+    <row r="358" ht="20.25" spans="1:13">
       <c r="A358" s="5" t="s">
         <v>373</v>
       </c>
@@ -12169,7 +11730,7 @@
       </c>
       <c r="M358" s="5"/>
     </row>
-    <row r="359" ht="19.6" spans="1:13">
+    <row r="359" ht="20.25" spans="1:13">
       <c r="A359" s="5" t="s">
         <v>374</v>
       </c>
@@ -12182,7 +11743,7 @@
       </c>
       <c r="M359" s="5"/>
     </row>
-    <row r="360" ht="19.6" spans="1:13">
+    <row r="360" ht="20.25" spans="1:13">
       <c r="A360" s="5" t="s">
         <v>375</v>
       </c>
@@ -12195,7 +11756,7 @@
       </c>
       <c r="M360" s="5"/>
     </row>
-    <row r="361" ht="19.6" spans="1:13">
+    <row r="361" ht="20.25" spans="1:13">
       <c r="A361" s="5" t="s">
         <v>376</v>
       </c>
@@ -12208,7 +11769,7 @@
       </c>
       <c r="M361" s="5"/>
     </row>
-    <row r="362" ht="19.6" spans="1:13">
+    <row r="362" ht="20.25" spans="1:13">
       <c r="A362" s="5" t="s">
         <v>377</v>
       </c>
@@ -12221,7 +11782,7 @@
       </c>
       <c r="M362" s="5"/>
     </row>
-    <row r="363" ht="19.6" spans="1:13">
+    <row r="363" ht="20.25" spans="1:13">
       <c r="A363" s="5" t="s">
         <v>378</v>
       </c>
@@ -12234,7 +11795,7 @@
       </c>
       <c r="M363" s="5"/>
     </row>
-    <row r="364" ht="19.6" spans="1:13">
+    <row r="364" ht="20.25" spans="1:13">
       <c r="A364" s="5" t="s">
         <v>379</v>
       </c>
@@ -12247,7 +11808,7 @@
       </c>
       <c r="M364" s="5"/>
     </row>
-    <row r="365" ht="19.6" spans="1:13">
+    <row r="365" ht="20.25" spans="1:13">
       <c r="A365" s="5" t="s">
         <v>380</v>
       </c>
@@ -12260,7 +11821,7 @@
       </c>
       <c r="M365" s="5"/>
     </row>
-    <row r="366" ht="19.6" spans="1:3">
+    <row r="366" ht="20.25" spans="1:13">
       <c r="A366" s="5" t="s">
         <v>381</v>
       </c>
@@ -12282,15 +11843,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F57"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.23008849557522" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.6153846153846" customWidth="1"/>
-    <col min="2" max="2" width="15.0576923076923" customWidth="1"/>
-    <col min="3" max="3" width="32.8461538461538" customWidth="1"/>
-    <col min="5" max="5" width="12.2307692307692" customWidth="1"/>
-    <col min="6" max="6" width="31.0769230769231" customWidth="1"/>
-    <col min="8" max="8" width="8.38461538461539"/>
-    <col min="9" max="9" width="27.8461538461538"/>
+    <col min="1" max="1" width="17.6194690265487" customWidth="1"/>
+    <col min="2" max="2" width="15.0619469026549" customWidth="1"/>
+    <col min="3" max="3" width="32.8495575221239" customWidth="1"/>
+    <col min="5" max="5" width="12.2300884955752" customWidth="1"/>
+    <col min="6" max="6" width="31.0796460176991" customWidth="1"/>
+    <col min="8" max="8" width="8.38053097345133"/>
+    <col min="9" max="9" width="27.8495575221239"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -12339,7 +11900,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" ht="13" customHeight="1" spans="1:6">
       <c r="A5" s="1">
         <v>44934</v>
       </c>
@@ -12348,7 +11909,7 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>44927</v>
       </c>
       <c r="F5" s="2">
@@ -12364,7 +11925,7 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>44958</v>
       </c>
       <c r="F6" s="2">
@@ -12380,7 +11941,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>44986</v>
       </c>
       <c r="F7" s="2">
@@ -12396,7 +11957,7 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>45017</v>
       </c>
       <c r="F8" s="2">
@@ -12412,7 +11973,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>45047</v>
       </c>
       <c r="F9" s="2">
@@ -12428,7 +11989,7 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>45078</v>
       </c>
       <c r="F10" s="2">
@@ -12444,7 +12005,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>45108</v>
       </c>
       <c r="F11" s="2">
@@ -12460,7 +12021,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>45139</v>
       </c>
       <c r="F12" s="2">
@@ -12476,7 +12037,7 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>45170</v>
       </c>
       <c r="F13" s="2">
@@ -12492,7 +12053,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>45200</v>
       </c>
       <c r="F14" s="2">
@@ -12508,7 +12069,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>45231</v>
       </c>
       <c r="F15" s="2">
@@ -12524,7 +12085,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>45261</v>
       </c>
       <c r="F16" s="2">
@@ -13015,8 +12576,8 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" ht="19.6" spans="3:3">
-      <c r="C57" s="3"/>
+    <row r="57" ht="20.25" spans="1:6">
+      <c r="C57" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
